--- a/data/nzd0287/nzd0287.xlsx
+++ b/data/nzd0287/nzd0287.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W355"/>
+  <dimension ref="A1:W356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27095,6 +27095,81 @@
       <c r="W355" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:54:26+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>349.52</v>
+      </c>
+      <c r="C356" t="n">
+        <v>346.25</v>
+      </c>
+      <c r="D356" t="n">
+        <v>355.77</v>
+      </c>
+      <c r="E356" t="n">
+        <v>346.96</v>
+      </c>
+      <c r="F356" t="n">
+        <v>348.13</v>
+      </c>
+      <c r="G356" t="n">
+        <v>358.42</v>
+      </c>
+      <c r="H356" t="n">
+        <v>353.52</v>
+      </c>
+      <c r="I356" t="n">
+        <v>363.94</v>
+      </c>
+      <c r="J356" t="n">
+        <v>361.15</v>
+      </c>
+      <c r="K356" t="n">
+        <v>351.76</v>
+      </c>
+      <c r="L356" t="n">
+        <v>353.43</v>
+      </c>
+      <c r="M356" t="n">
+        <v>362.68</v>
+      </c>
+      <c r="N356" t="n">
+        <v>365.66</v>
+      </c>
+      <c r="O356" t="n">
+        <v>365.92</v>
+      </c>
+      <c r="P356" t="n">
+        <v>374.47</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>372.49</v>
+      </c>
+      <c r="R356" t="n">
+        <v>381.53</v>
+      </c>
+      <c r="S356" t="n">
+        <v>378.04</v>
+      </c>
+      <c r="T356" t="n">
+        <v>368.53</v>
+      </c>
+      <c r="U356" t="n">
+        <v>357.35</v>
+      </c>
+      <c r="V356" t="n">
+        <v>356.09</v>
+      </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -27109,7 +27184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B357"/>
+  <dimension ref="A1:B358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30682,6 +30757,16 @@
       </c>
       <c r="B357" t="n">
         <v>0.73</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>-0.65</v>
       </c>
     </row>
   </sheetData>
@@ -30850,28 +30935,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.11960653901468</v>
+        <v>-0.1227023825305367</v>
       </c>
       <c r="J2" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K2" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05798153017908581</v>
+        <v>0.06087788181007869</v>
       </c>
       <c r="M2" t="n">
-        <v>2.676163337653763</v>
+        <v>2.681370782374697</v>
       </c>
       <c r="N2" t="n">
-        <v>12.34361557365533</v>
+        <v>12.38384281181348</v>
       </c>
       <c r="O2" t="n">
-        <v>3.51334819988787</v>
+        <v>3.519068457960641</v>
       </c>
       <c r="P2" t="n">
-        <v>357.8461701435793</v>
+        <v>357.8779442069158</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30928,28 +31013,28 @@
         <v>0.0311</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0851749733421109</v>
+        <v>-0.08758239426322519</v>
       </c>
       <c r="J3" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K3" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02836573573066747</v>
+        <v>0.03004066429767704</v>
       </c>
       <c r="M3" t="n">
-        <v>2.826961033173542</v>
+        <v>2.829441743303352</v>
       </c>
       <c r="N3" t="n">
-        <v>13.19761870217717</v>
+        <v>13.20579422982257</v>
       </c>
       <c r="O3" t="n">
-        <v>3.632852694808471</v>
+        <v>3.633977742064825</v>
       </c>
       <c r="P3" t="n">
-        <v>352.5249311762929</v>
+        <v>352.5496396424778</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31006,28 +31091,28 @@
         <v>0.0361</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08959445587907675</v>
+        <v>0.08873327990167068</v>
       </c>
       <c r="J4" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K4" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02855132099197</v>
+        <v>0.02819494697100167</v>
       </c>
       <c r="M4" t="n">
-        <v>2.986294665271204</v>
+        <v>2.982015783917983</v>
       </c>
       <c r="N4" t="n">
-        <v>14.50503305988357</v>
+        <v>14.46997711707709</v>
       </c>
       <c r="O4" t="n">
-        <v>3.808547368733067</v>
+        <v>3.803942312532762</v>
       </c>
       <c r="P4" t="n">
-        <v>354.8551787205079</v>
+        <v>354.8640173649387</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31084,28 +31169,28 @@
         <v>0.0411</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07822241236778704</v>
+        <v>0.07796035768693678</v>
       </c>
       <c r="J5" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K5" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02037049194971463</v>
+        <v>0.02037138609964251</v>
       </c>
       <c r="M5" t="n">
-        <v>3.153118922345096</v>
+        <v>3.145502996578764</v>
       </c>
       <c r="N5" t="n">
-        <v>15.62735747694668</v>
+        <v>15.58387412416798</v>
       </c>
       <c r="O5" t="n">
-        <v>3.953145263830648</v>
+        <v>3.947641590135556</v>
       </c>
       <c r="P5" t="n">
-        <v>345.3440358784049</v>
+        <v>345.3467254659064</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31162,28 +31247,28 @@
         <v>0.0456</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1435532919683746</v>
+        <v>0.144185270683002</v>
       </c>
       <c r="J6" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K6" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0800504045838023</v>
+        <v>0.08118641750825029</v>
       </c>
       <c r="M6" t="n">
-        <v>2.859240323370404</v>
+        <v>2.85396229160607</v>
       </c>
       <c r="N6" t="n">
-        <v>12.57736339199909</v>
+        <v>12.54505953383066</v>
       </c>
       <c r="O6" t="n">
-        <v>3.546457865532748</v>
+        <v>3.541900553916027</v>
       </c>
       <c r="P6" t="n">
-        <v>343.2952033569603</v>
+        <v>343.2887170692641</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31240,28 +31325,28 @@
         <v>0.0468</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1474428096778948</v>
+        <v>0.1471497135047924</v>
       </c>
       <c r="J7" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K7" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09665628315546759</v>
+        <v>0.09689654253861357</v>
       </c>
       <c r="M7" t="n">
-        <v>2.750080013091259</v>
+        <v>2.743617790213847</v>
       </c>
       <c r="N7" t="n">
-        <v>10.79028533166903</v>
+        <v>10.76056238244492</v>
       </c>
       <c r="O7" t="n">
-        <v>3.284856972787253</v>
+        <v>3.280329614908374</v>
       </c>
       <c r="P7" t="n">
-        <v>355.0366771298362</v>
+        <v>355.0396853104241</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31318,28 +31403,28 @@
         <v>0.0413</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01140895350586673</v>
+        <v>0.009944446926534624</v>
       </c>
       <c r="J8" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K8" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005433271915974425</v>
+        <v>0.0004151084427431728</v>
       </c>
       <c r="M8" t="n">
-        <v>2.80766705229951</v>
+        <v>2.806001989795844</v>
       </c>
       <c r="N8" t="n">
-        <v>12.71618820469184</v>
+        <v>12.69715113635373</v>
       </c>
       <c r="O8" t="n">
-        <v>3.565976472818047</v>
+        <v>3.563306208614933</v>
       </c>
       <c r="P8" t="n">
-        <v>355.6694671684535</v>
+        <v>355.6844980718471</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31396,28 +31481,28 @@
         <v>0.0415</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04362891443613677</v>
+        <v>0.03987747233506771</v>
       </c>
       <c r="J9" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K9" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L9" t="n">
-        <v>0.007212708182337324</v>
+        <v>0.006026143316056554</v>
       </c>
       <c r="M9" t="n">
-        <v>3.123736580323</v>
+        <v>3.129022227587836</v>
       </c>
       <c r="N9" t="n">
-        <v>13.91455933663631</v>
+        <v>13.98548894664686</v>
       </c>
       <c r="O9" t="n">
-        <v>3.730222424552764</v>
+        <v>3.73971776296646</v>
       </c>
       <c r="P9" t="n">
-        <v>369.073749212658</v>
+        <v>369.1122519852666</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31474,28 +31559,28 @@
         <v>0.0443</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07762176074800238</v>
+        <v>0.07431479714662274</v>
       </c>
       <c r="J10" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K10" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01806277014628344</v>
+        <v>0.01661196777096885</v>
       </c>
       <c r="M10" t="n">
-        <v>3.455393969033651</v>
+        <v>3.459260135120264</v>
       </c>
       <c r="N10" t="n">
-        <v>17.39518876688959</v>
+        <v>17.43176392939465</v>
       </c>
       <c r="O10" t="n">
-        <v>4.170753980623839</v>
+        <v>4.175136396501873</v>
       </c>
       <c r="P10" t="n">
-        <v>364.6459172800696</v>
+        <v>364.6798581657713</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31552,28 +31637,28 @@
         <v>0.0429</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0692124924866211</v>
+        <v>0.06639157354911447</v>
       </c>
       <c r="J11" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K11" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02307104727446441</v>
+        <v>0.02128897765125193</v>
       </c>
       <c r="M11" t="n">
-        <v>2.620638502183985</v>
+        <v>2.625804798550482</v>
       </c>
       <c r="N11" t="n">
-        <v>10.77277143274349</v>
+        <v>10.8046947300477</v>
       </c>
       <c r="O11" t="n">
-        <v>3.282190036049632</v>
+        <v>3.287049547854078</v>
       </c>
       <c r="P11" t="n">
-        <v>354.6640543466689</v>
+        <v>354.6930067328371</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31630,28 +31715,28 @@
         <v>0.0355</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01223062184251907</v>
+        <v>0.009778480818105287</v>
       </c>
       <c r="J12" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K12" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0006041987881423294</v>
+        <v>0.0003875361530036869</v>
       </c>
       <c r="M12" t="n">
-        <v>2.884680321792926</v>
+        <v>2.889218515498558</v>
       </c>
       <c r="N12" t="n">
-        <v>13.14067101597357</v>
+        <v>13.15070751792337</v>
       </c>
       <c r="O12" t="n">
-        <v>3.625006347025281</v>
+        <v>3.62639042546764</v>
       </c>
       <c r="P12" t="n">
-        <v>357.2174563929037</v>
+        <v>357.2426238420401</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31708,28 +31793,28 @@
         <v>0.0256</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1430187137487381</v>
+        <v>-0.1447727330740186</v>
       </c>
       <c r="J13" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K13" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04373630361494829</v>
+        <v>0.04501494886479962</v>
       </c>
       <c r="M13" t="n">
-        <v>3.717606024029961</v>
+        <v>3.716047299760292</v>
       </c>
       <c r="N13" t="n">
-        <v>23.75112162221923</v>
+        <v>23.70829172463726</v>
       </c>
       <c r="O13" t="n">
-        <v>4.873512247057477</v>
+        <v>4.869116113283525</v>
       </c>
       <c r="P13" t="n">
-        <v>369.3743156929004</v>
+        <v>369.3923179985239</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31786,28 +31871,28 @@
         <v>0.0262</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.02963861854247757</v>
+        <v>-0.03054793855078973</v>
       </c>
       <c r="J14" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K14" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L14" t="n">
-        <v>0.00258237350351842</v>
+        <v>0.002760465028456061</v>
       </c>
       <c r="M14" t="n">
-        <v>3.405320796472944</v>
+        <v>3.399721948729941</v>
       </c>
       <c r="N14" t="n">
-        <v>18.01924920220565</v>
+        <v>17.97496106385633</v>
       </c>
       <c r="O14" t="n">
-        <v>4.2449086211844</v>
+        <v>4.239688793279093</v>
       </c>
       <c r="P14" t="n">
-        <v>367.9607652356018</v>
+        <v>367.9700980043252</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31864,28 +31949,28 @@
         <v>0.0255</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1193236648932544</v>
+        <v>-0.1210679681232516</v>
       </c>
       <c r="J15" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K15" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03883854551824417</v>
+        <v>0.04014868799145788</v>
       </c>
       <c r="M15" t="n">
-        <v>3.385733041582891</v>
+        <v>3.384101439245554</v>
       </c>
       <c r="N15" t="n">
-        <v>18.71325566531024</v>
+        <v>18.68435096296851</v>
       </c>
       <c r="O15" t="n">
-        <v>4.325882067892079</v>
+        <v>4.322539874075023</v>
       </c>
       <c r="P15" t="n">
-        <v>371.9763692024</v>
+        <v>371.9942717872768</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31942,28 +32027,28 @@
         <v>0.0261</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1242694096188103</v>
+        <v>-0.12521523695768</v>
       </c>
       <c r="J16" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K16" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03954058751074008</v>
+        <v>0.04036921917035807</v>
       </c>
       <c r="M16" t="n">
-        <v>3.69768841071197</v>
+        <v>3.69157298017371</v>
       </c>
       <c r="N16" t="n">
-        <v>19.92173525066251</v>
+        <v>19.87261796522319</v>
       </c>
       <c r="O16" t="n">
-        <v>4.463377112754703</v>
+        <v>4.457871461271981</v>
       </c>
       <c r="P16" t="n">
-        <v>379.3202324594079</v>
+        <v>379.3299399196257</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32020,28 +32105,28 @@
         <v>0.0267</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1577171445913063</v>
+        <v>-0.1581304264411774</v>
       </c>
       <c r="J17" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K17" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L17" t="n">
-        <v>0.07190440953486665</v>
+        <v>0.07270571258974734</v>
       </c>
       <c r="M17" t="n">
-        <v>3.325321820504324</v>
+        <v>3.31793456131287</v>
       </c>
       <c r="N17" t="n">
-        <v>17.05131162486574</v>
+        <v>17.00461630823083</v>
       </c>
       <c r="O17" t="n">
-        <v>4.129323385842497</v>
+        <v>4.123665397220152</v>
       </c>
       <c r="P17" t="n">
-        <v>377.3319213396193</v>
+        <v>377.3361630409865</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32098,28 +32183,28 @@
         <v>0.0328</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.02860564613704325</v>
+        <v>-0.02886978843549327</v>
       </c>
       <c r="J18" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K18" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002763418577664378</v>
+        <v>0.002833569295518035</v>
       </c>
       <c r="M18" t="n">
-        <v>3.091211135931347</v>
+        <v>3.083813655759706</v>
       </c>
       <c r="N18" t="n">
-        <v>15.6825921210813</v>
+        <v>15.63896177364677</v>
       </c>
       <c r="O18" t="n">
-        <v>3.960125265832041</v>
+        <v>3.954612721069759</v>
       </c>
       <c r="P18" t="n">
-        <v>382.7197776643958</v>
+        <v>382.7224886780753</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32176,28 +32261,28 @@
         <v>0.033</v>
       </c>
       <c r="I19" t="n">
-        <v>0.003209335221616518</v>
+        <v>0.002651893328858462</v>
       </c>
       <c r="J19" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K19" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L19" t="n">
-        <v>2.736268977732159e-05</v>
+        <v>1.88079155423182e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.185973609444836</v>
+        <v>3.179518155136074</v>
       </c>
       <c r="N19" t="n">
-        <v>19.99043706762199</v>
+        <v>19.93655756986636</v>
       </c>
       <c r="O19" t="n">
-        <v>4.471066658821135</v>
+        <v>4.46503724171102</v>
       </c>
       <c r="P19" t="n">
-        <v>378.8881064053421</v>
+        <v>378.8938276874147</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32254,28 +32339,28 @@
         <v>0.036</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03619501426185497</v>
+        <v>0.03514343965796063</v>
       </c>
       <c r="J20" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K20" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L20" t="n">
-        <v>0.003628601640421447</v>
+        <v>0.003443206789781494</v>
       </c>
       <c r="M20" t="n">
-        <v>3.318580951815114</v>
+        <v>3.313707131509771</v>
       </c>
       <c r="N20" t="n">
-        <v>19.10478958886568</v>
+        <v>19.05962638130036</v>
       </c>
       <c r="O20" t="n">
-        <v>4.37090260574011</v>
+        <v>4.365733200883943</v>
       </c>
       <c r="P20" t="n">
-        <v>369.3442305355229</v>
+        <v>369.3550233284712</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32332,28 +32417,28 @@
         <v>0.0526</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1092817397137091</v>
+        <v>0.1076518792526877</v>
       </c>
       <c r="J21" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K21" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L21" t="n">
-        <v>0.04185302259543544</v>
+        <v>0.04087376459056091</v>
       </c>
       <c r="M21" t="n">
-        <v>2.893641809587846</v>
+        <v>2.892335192578016</v>
       </c>
       <c r="N21" t="n">
-        <v>14.51988916843742</v>
+        <v>14.4997751025329</v>
       </c>
       <c r="O21" t="n">
-        <v>3.810497233752757</v>
+        <v>3.807857022333284</v>
       </c>
       <c r="P21" t="n">
-        <v>357.2028542309124</v>
+        <v>357.2195822371093</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32410,28 +32495,28 @@
         <v>0.0488</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.004755344918745578</v>
+        <v>-0.007413740921016475</v>
       </c>
       <c r="J22" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K22" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L22" t="n">
-        <v>8.677615099272895e-05</v>
+        <v>0.0002114799740952078</v>
       </c>
       <c r="M22" t="n">
-        <v>2.72487263008533</v>
+        <v>2.727690123060501</v>
       </c>
       <c r="N22" t="n">
-        <v>13.83849210332317</v>
+        <v>13.85481117657468</v>
       </c>
       <c r="O22" t="n">
-        <v>3.720012379458322</v>
+        <v>3.722205149716318</v>
       </c>
       <c r="P22" t="n">
-        <v>360.6659947136137</v>
+        <v>360.6932790522818</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32469,7 +32554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W355"/>
+  <dimension ref="A1:W356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74007,6 +74092,123 @@
         </is>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:54:26+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-39.19700801025528,177.9201694871754</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>-39.197609926885384,177.91971395203774</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-39.198262162811815,177.9193914876869</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-39.198835884481674,177.9188708873241</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-39.19943704756376,177.9184120210229</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-39.20009657132545,177.91816460688432</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-39.20077598878301,177.91797321994832</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-39.20147492646035,177.9179623978916</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-39.202161126184485,177.9178019754489</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>-39.20283794985939,177.91756911493428</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>-39.203486497968186,177.91726760197312</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>-39.204156642759266,177.9170160301784</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>-39.204804778710646,177.9166966809922</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>-39.20545389393115,177.91638193255224</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>-39.20613083025795,177.91616726795692</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>-39.20677855091555,177.915836916949</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>-39.207455885876385,177.9156334770425</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>-39.20810387113899,177.91530605427772</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>-39.20873824317975,177.9149114515932</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>-39.209368443898185,177.91449846724453</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>-39.21002126574977,177.91418468691518</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0287/nzd0287.xlsx
+++ b/data/nzd0287/nzd0287.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W356"/>
+  <dimension ref="A1:W357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27168,6 +27168,81 @@
         <v>356.09</v>
       </c>
       <c r="W356" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:54:28+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>348.66</v>
+      </c>
+      <c r="C357" t="n">
+        <v>345.59</v>
+      </c>
+      <c r="D357" t="n">
+        <v>354.89</v>
+      </c>
+      <c r="E357" t="n">
+        <v>345.21</v>
+      </c>
+      <c r="F357" t="n">
+        <v>347.47</v>
+      </c>
+      <c r="G357" t="n">
+        <v>357.1</v>
+      </c>
+      <c r="H357" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="I357" t="n">
+        <v>362.31</v>
+      </c>
+      <c r="J357" t="n">
+        <v>359.94</v>
+      </c>
+      <c r="K357" t="n">
+        <v>351.01</v>
+      </c>
+      <c r="L357" t="n">
+        <v>351.45</v>
+      </c>
+      <c r="M357" t="n">
+        <v>362.57</v>
+      </c>
+      <c r="N357" t="n">
+        <v>364.94</v>
+      </c>
+      <c r="O357" t="n">
+        <v>365.02</v>
+      </c>
+      <c r="P357" t="n">
+        <v>373.84</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>371.96</v>
+      </c>
+      <c r="R357" t="n">
+        <v>381.02</v>
+      </c>
+      <c r="S357" t="n">
+        <v>378.15</v>
+      </c>
+      <c r="T357" t="n">
+        <v>368.41</v>
+      </c>
+      <c r="U357" t="n">
+        <v>356.16</v>
+      </c>
+      <c r="V357" t="n">
+        <v>355.32</v>
+      </c>
+      <c r="W357" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27184,7 +27259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30767,6 +30842,16 @@
       </c>
       <c r="B358" t="n">
         <v>-0.65</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -30935,28 +31020,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1227023825305367</v>
+        <v>-0.1262542862357675</v>
       </c>
       <c r="J2" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K2" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06087788181007869</v>
+        <v>0.06414735016817785</v>
       </c>
       <c r="M2" t="n">
-        <v>2.681370782374697</v>
+        <v>2.688730298627827</v>
       </c>
       <c r="N2" t="n">
-        <v>12.38384281181348</v>
+        <v>12.44863481445584</v>
       </c>
       <c r="O2" t="n">
-        <v>3.519068457960641</v>
+        <v>3.528262293885737</v>
       </c>
       <c r="P2" t="n">
-        <v>357.8779442069158</v>
+        <v>357.9144637189983</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31013,28 +31098,28 @@
         <v>0.0311</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08758239426322519</v>
+        <v>-0.0903432097602429</v>
       </c>
       <c r="J3" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K3" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03004066429767704</v>
+        <v>0.03197110379188539</v>
       </c>
       <c r="M3" t="n">
-        <v>2.829441743303352</v>
+        <v>2.833589945832175</v>
       </c>
       <c r="N3" t="n">
-        <v>13.20579422982257</v>
+        <v>13.22886045383022</v>
       </c>
       <c r="O3" t="n">
-        <v>3.633977742064825</v>
+        <v>3.637150045548055</v>
       </c>
       <c r="P3" t="n">
-        <v>352.5496396424778</v>
+        <v>352.5780254443654</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31091,28 +31176,28 @@
         <v>0.0361</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08873327990167068</v>
+        <v>0.08735951139621911</v>
       </c>
       <c r="J4" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K4" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02819494697100167</v>
+        <v>0.02750515550856469</v>
       </c>
       <c r="M4" t="n">
-        <v>2.982015783917983</v>
+        <v>2.980204355940839</v>
       </c>
       <c r="N4" t="n">
-        <v>14.46997711707709</v>
+        <v>14.44422707348618</v>
       </c>
       <c r="O4" t="n">
-        <v>3.803942312532762</v>
+        <v>3.800556153181555</v>
       </c>
       <c r="P4" t="n">
-        <v>354.8640173649387</v>
+        <v>354.8781420033571</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31169,28 +31254,28 @@
         <v>0.0411</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07796035768693678</v>
+        <v>0.07665911850617667</v>
       </c>
       <c r="J5" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K5" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02037138609964251</v>
+        <v>0.01982462669120744</v>
       </c>
       <c r="M5" t="n">
-        <v>3.145502996578764</v>
+        <v>3.142984566673069</v>
       </c>
       <c r="N5" t="n">
-        <v>15.58387412416798</v>
+        <v>15.55346378673102</v>
       </c>
       <c r="O5" t="n">
-        <v>3.947641590135556</v>
+        <v>3.943787999719435</v>
       </c>
       <c r="P5" t="n">
-        <v>345.3467254659064</v>
+        <v>345.3601043815324</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31247,28 +31332,28 @@
         <v>0.0456</v>
       </c>
       <c r="I6" t="n">
-        <v>0.144185270683002</v>
+        <v>0.1444110547775819</v>
       </c>
       <c r="J6" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K6" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08118641750825029</v>
+        <v>0.08192469738294694</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85396229160607</v>
+        <v>2.846930288377239</v>
       </c>
       <c r="N6" t="n">
-        <v>12.54505953383066</v>
+        <v>12.51022297484358</v>
       </c>
       <c r="O6" t="n">
-        <v>3.541900553916027</v>
+        <v>3.536979357424012</v>
       </c>
       <c r="P6" t="n">
-        <v>343.2887170692641</v>
+        <v>343.2863956310568</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31325,28 +31410,28 @@
         <v>0.0468</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1471497135047924</v>
+        <v>0.1460743698359996</v>
       </c>
       <c r="J7" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K7" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09689654253861357</v>
+        <v>0.09613264256650267</v>
       </c>
       <c r="M7" t="n">
-        <v>2.743617790213847</v>
+        <v>2.740593022914085</v>
       </c>
       <c r="N7" t="n">
-        <v>10.76056238244492</v>
+        <v>10.73946324937727</v>
       </c>
       <c r="O7" t="n">
-        <v>3.280329614908374</v>
+        <v>3.277112028810927</v>
       </c>
       <c r="P7" t="n">
-        <v>355.0396853104241</v>
+        <v>355.0507416422857</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31403,28 +31488,28 @@
         <v>0.0413</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009944446926534624</v>
+        <v>0.006500883822640979</v>
       </c>
       <c r="J8" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K8" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004151084427431728</v>
+        <v>0.0001773312514063985</v>
       </c>
       <c r="M8" t="n">
-        <v>2.806001989795844</v>
+        <v>2.812755628825083</v>
       </c>
       <c r="N8" t="n">
-        <v>12.69715113635373</v>
+        <v>12.75508101940057</v>
       </c>
       <c r="O8" t="n">
-        <v>3.563306208614933</v>
+        <v>3.571425628429153</v>
       </c>
       <c r="P8" t="n">
-        <v>355.6844980718471</v>
+        <v>355.7199036613044</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31481,28 +31566,28 @@
         <v>0.0415</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03987747233506771</v>
+        <v>0.03521261065632582</v>
       </c>
       <c r="J9" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K9" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006026143316056554</v>
+        <v>0.00467937806898322</v>
       </c>
       <c r="M9" t="n">
-        <v>3.129022227587836</v>
+        <v>3.137625454667177</v>
       </c>
       <c r="N9" t="n">
-        <v>13.98548894664686</v>
+        <v>14.11796263252613</v>
       </c>
       <c r="O9" t="n">
-        <v>3.73971776296646</v>
+        <v>3.757387740508841</v>
       </c>
       <c r="P9" t="n">
-        <v>369.1122519852666</v>
+        <v>369.1602145671881</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31559,28 +31644,28 @@
         <v>0.0443</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07431479714662274</v>
+        <v>0.07033612181837462</v>
       </c>
       <c r="J10" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K10" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01661196777096885</v>
+        <v>0.01490072438417189</v>
       </c>
       <c r="M10" t="n">
-        <v>3.459260135120264</v>
+        <v>3.465855127095703</v>
       </c>
       <c r="N10" t="n">
-        <v>17.43176392939465</v>
+        <v>17.50774315458739</v>
       </c>
       <c r="O10" t="n">
-        <v>4.175136396501873</v>
+        <v>4.18422551430816</v>
       </c>
       <c r="P10" t="n">
-        <v>364.6798581657713</v>
+        <v>364.7207656040862</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31637,28 +31722,28 @@
         <v>0.0429</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06639157354911447</v>
+        <v>0.06316940446793967</v>
       </c>
       <c r="J11" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K11" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02128897765125193</v>
+        <v>0.01929614819081782</v>
       </c>
       <c r="M11" t="n">
-        <v>2.625804798550482</v>
+        <v>2.632775313470153</v>
       </c>
       <c r="N11" t="n">
-        <v>10.8046947300477</v>
+        <v>10.85629240094982</v>
       </c>
       <c r="O11" t="n">
-        <v>3.287049547854078</v>
+        <v>3.294888829831716</v>
       </c>
       <c r="P11" t="n">
-        <v>354.6930067328371</v>
+        <v>354.72613602137</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31715,28 +31800,28 @@
         <v>0.0355</v>
       </c>
       <c r="I12" t="n">
-        <v>0.009778480818105287</v>
+        <v>0.00618722810392335</v>
       </c>
       <c r="J12" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K12" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0003875361530036869</v>
+        <v>0.0001550386323281305</v>
       </c>
       <c r="M12" t="n">
-        <v>2.889218515498558</v>
+        <v>2.899928922712407</v>
       </c>
       <c r="N12" t="n">
-        <v>13.15070751792337</v>
+        <v>13.21556393635571</v>
       </c>
       <c r="O12" t="n">
-        <v>3.62639042546764</v>
+        <v>3.635321710159324</v>
       </c>
       <c r="P12" t="n">
-        <v>357.2426238420401</v>
+        <v>357.2795479277617</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31793,28 +31878,28 @@
         <v>0.0256</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1447727330740186</v>
+        <v>-0.1465577727583039</v>
       </c>
       <c r="J13" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K13" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04501494886479962</v>
+        <v>0.04633141133835483</v>
       </c>
       <c r="M13" t="n">
-        <v>3.716047299760292</v>
+        <v>3.714728211683604</v>
       </c>
       <c r="N13" t="n">
-        <v>23.70829172463726</v>
+        <v>23.66684534946018</v>
       </c>
       <c r="O13" t="n">
-        <v>4.869116113283525</v>
+        <v>4.864858204455725</v>
       </c>
       <c r="P13" t="n">
-        <v>369.3923179985239</v>
+        <v>369.4106711926777</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31871,28 +31956,28 @@
         <v>0.0262</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.03054793855078973</v>
+        <v>-0.03186691197702633</v>
       </c>
       <c r="J14" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K14" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002760465028456061</v>
+        <v>0.003021257118345222</v>
       </c>
       <c r="M14" t="n">
-        <v>3.399721948729941</v>
+        <v>3.395928921969675</v>
       </c>
       <c r="N14" t="n">
-        <v>17.97496106385633</v>
+        <v>17.93820095738229</v>
       </c>
       <c r="O14" t="n">
-        <v>4.239688793279093</v>
+        <v>4.235351338127959</v>
       </c>
       <c r="P14" t="n">
-        <v>367.9700980043252</v>
+        <v>367.9836592576624</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31949,28 +32034,28 @@
         <v>0.0255</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1210679681232516</v>
+        <v>-0.1233179887893545</v>
       </c>
       <c r="J15" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K15" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04014868799145788</v>
+        <v>0.04177664341133236</v>
       </c>
       <c r="M15" t="n">
-        <v>3.384101439245554</v>
+        <v>3.384931649332463</v>
       </c>
       <c r="N15" t="n">
-        <v>18.68435096296851</v>
+        <v>18.67182581042341</v>
       </c>
       <c r="O15" t="n">
-        <v>4.322539874075023</v>
+        <v>4.321090812563814</v>
       </c>
       <c r="P15" t="n">
-        <v>371.9942717872768</v>
+        <v>372.0174057637921</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32027,28 +32112,28 @@
         <v>0.0261</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.12521523695768</v>
+        <v>-0.1265157745175576</v>
       </c>
       <c r="J16" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K16" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L16" t="n">
-        <v>0.04036921917035807</v>
+        <v>0.04141839298712813</v>
       </c>
       <c r="M16" t="n">
-        <v>3.69157298017371</v>
+        <v>3.687076789944598</v>
       </c>
       <c r="N16" t="n">
-        <v>19.87261796522319</v>
+        <v>19.83014618618623</v>
       </c>
       <c r="O16" t="n">
-        <v>4.457871461271981</v>
+        <v>4.453105229633163</v>
       </c>
       <c r="P16" t="n">
-        <v>379.3299399196257</v>
+        <v>379.3433116214152</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32105,28 +32190,28 @@
         <v>0.0267</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1581304264411774</v>
+        <v>-0.1588497721624517</v>
       </c>
       <c r="J17" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K17" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L17" t="n">
-        <v>0.07270571258974734</v>
+        <v>0.07376420708664311</v>
       </c>
       <c r="M17" t="n">
-        <v>3.31793456131287</v>
+        <v>3.312038457628717</v>
       </c>
       <c r="N17" t="n">
-        <v>17.00461630823083</v>
+        <v>16.96093482331884</v>
       </c>
       <c r="O17" t="n">
-        <v>4.123665397220152</v>
+        <v>4.118365552415041</v>
       </c>
       <c r="P17" t="n">
-        <v>377.3361630409865</v>
+        <v>377.3435591183973</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32183,28 +32268,28 @@
         <v>0.0328</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.02886978843549327</v>
+        <v>-0.02942677514015625</v>
       </c>
       <c r="J18" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K18" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002833569295518035</v>
+        <v>0.002963076306643164</v>
       </c>
       <c r="M18" t="n">
-        <v>3.083813655759706</v>
+        <v>3.077896770910347</v>
       </c>
       <c r="N18" t="n">
-        <v>15.63896177364677</v>
+        <v>15.59748078008291</v>
       </c>
       <c r="O18" t="n">
-        <v>3.954612721069759</v>
+        <v>3.949364604601974</v>
       </c>
       <c r="P18" t="n">
-        <v>382.7224886780753</v>
+        <v>382.7282154331842</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32261,28 +32346,28 @@
         <v>0.033</v>
       </c>
       <c r="I19" t="n">
-        <v>0.002651893328858462</v>
+        <v>0.002168822868394781</v>
       </c>
       <c r="J19" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K19" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L19" t="n">
-        <v>1.88079155423182e-05</v>
+        <v>1.266410838107745e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.179518155136074</v>
+        <v>3.172760442633782</v>
       </c>
       <c r="N19" t="n">
-        <v>19.93655756986636</v>
+        <v>19.88239788791493</v>
       </c>
       <c r="O19" t="n">
-        <v>4.46503724171102</v>
+        <v>4.458968253746032</v>
       </c>
       <c r="P19" t="n">
-        <v>378.8938276874147</v>
+        <v>378.8987944598786</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32339,28 +32424,28 @@
         <v>0.036</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03514343965796063</v>
+        <v>0.03403559398065421</v>
       </c>
       <c r="J20" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K20" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L20" t="n">
-        <v>0.003443206789781494</v>
+        <v>0.003250419417313521</v>
       </c>
       <c r="M20" t="n">
-        <v>3.313707131509771</v>
+        <v>3.309098651766631</v>
       </c>
       <c r="N20" t="n">
-        <v>19.05962638130036</v>
+        <v>19.01577534156609</v>
       </c>
       <c r="O20" t="n">
-        <v>4.365733200883943</v>
+        <v>4.360708123867738</v>
       </c>
       <c r="P20" t="n">
-        <v>369.3550233284712</v>
+        <v>369.366413835353</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32417,28 +32502,28 @@
         <v>0.0526</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1076518792526877</v>
+        <v>0.1053401123477687</v>
       </c>
       <c r="J21" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K21" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L21" t="n">
-        <v>0.04087376459056091</v>
+        <v>0.03935034353979139</v>
       </c>
       <c r="M21" t="n">
-        <v>2.892335192578016</v>
+        <v>2.894047465254377</v>
       </c>
       <c r="N21" t="n">
-        <v>14.4997751025329</v>
+        <v>14.50122761958871</v>
       </c>
       <c r="O21" t="n">
-        <v>3.807857022333284</v>
+        <v>3.808047743869385</v>
       </c>
       <c r="P21" t="n">
-        <v>357.2195822371093</v>
+        <v>357.2433510682552</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32495,28 +32580,28 @@
         <v>0.0488</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.007413740921016475</v>
+        <v>-0.0104897346655246</v>
       </c>
       <c r="J22" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K22" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0002114799740952078</v>
+        <v>0.0004238628832334834</v>
       </c>
       <c r="M22" t="n">
-        <v>2.727690123060501</v>
+        <v>2.732332072991292</v>
       </c>
       <c r="N22" t="n">
-        <v>13.85481117657468</v>
+        <v>13.89057453635063</v>
       </c>
       <c r="O22" t="n">
-        <v>3.722205149716318</v>
+        <v>3.727006108976832</v>
       </c>
       <c r="P22" t="n">
-        <v>360.6932790522818</v>
+        <v>360.7249054138164</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32554,7 +32639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W356"/>
+  <dimension ref="A1:W357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74209,6 +74294,123 @@
         </is>
       </c>
     </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:54:28+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>-39.19700463241276,177.92016054829202</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>-39.197607334571316,177.91970709191241</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-39.198258662010595,177.9193823686863</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-39.198828504706036,177.91885302785323</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-39.199434499133865,177.91840513360467</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-39.2000937221709,177.91814979975675</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-39.20077262802093,177.91793451800768</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-39.2014733381206,177.91794367309572</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-39.20215995989115,177.91778807352813</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-39.202836473759405,177.91756065820346</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-39.203480388075725,177.91724611087287</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>-39.20415628861103,177.91701484329573</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>-39.20480258352236,177.91668885349148</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>-39.20545134734739,177.91637206030993</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>-39.20612907755351,177.91616034469388</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>-39.20677708990908,177.91583108694704</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>-39.207454529919836,177.91562784672192</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>-39.20810415561938,177.9153072718003</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>-39.20873793283461,177.9149101233754</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>-39.20936530205514,177.91448532071527</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>-39.21001919130324,177.9141761968215</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0287/nzd0287.xlsx
+++ b/data/nzd0287/nzd0287.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W357"/>
+  <dimension ref="A1:W359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27243,6 +27243,156 @@
         <v>355.32</v>
       </c>
       <c r="W357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:03+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>353.51</v>
+      </c>
+      <c r="C358" t="n">
+        <v>350.18</v>
+      </c>
+      <c r="D358" t="n">
+        <v>356.43</v>
+      </c>
+      <c r="E358" t="n">
+        <v>347.6</v>
+      </c>
+      <c r="F358" t="n">
+        <v>349.44</v>
+      </c>
+      <c r="G358" t="n">
+        <v>357.49</v>
+      </c>
+      <c r="H358" t="n">
+        <v>349.98</v>
+      </c>
+      <c r="I358" t="n">
+        <v>363.96</v>
+      </c>
+      <c r="J358" t="n">
+        <v>362.07</v>
+      </c>
+      <c r="K358" t="n">
+        <v>353.62</v>
+      </c>
+      <c r="L358" t="n">
+        <v>352.72</v>
+      </c>
+      <c r="M358" t="n">
+        <v>366.75</v>
+      </c>
+      <c r="N358" t="n">
+        <v>368.2</v>
+      </c>
+      <c r="O358" t="n">
+        <v>368.87</v>
+      </c>
+      <c r="P358" t="n">
+        <v>372.73</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>374.53</v>
+      </c>
+      <c r="R358" t="n">
+        <v>383.06</v>
+      </c>
+      <c r="S358" t="n">
+        <v>381.06</v>
+      </c>
+      <c r="T358" t="n">
+        <v>371.5</v>
+      </c>
+      <c r="U358" t="n">
+        <v>358.55</v>
+      </c>
+      <c r="V358" t="n">
+        <v>355.03</v>
+      </c>
+      <c r="W358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:54:09+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>353.7</v>
+      </c>
+      <c r="C359" t="n">
+        <v>350.89</v>
+      </c>
+      <c r="D359" t="n">
+        <v>356.41</v>
+      </c>
+      <c r="E359" t="n">
+        <v>348.6</v>
+      </c>
+      <c r="F359" t="n">
+        <v>349.04</v>
+      </c>
+      <c r="G359" t="n">
+        <v>358.15</v>
+      </c>
+      <c r="H359" t="n">
+        <v>350.8</v>
+      </c>
+      <c r="I359" t="n">
+        <v>364.54</v>
+      </c>
+      <c r="J359" t="n">
+        <v>362.21</v>
+      </c>
+      <c r="K359" t="n">
+        <v>354.01</v>
+      </c>
+      <c r="L359" t="n">
+        <v>353.21</v>
+      </c>
+      <c r="M359" t="n">
+        <v>368.12</v>
+      </c>
+      <c r="N359" t="n">
+        <v>368.51</v>
+      </c>
+      <c r="O359" t="n">
+        <v>369.95</v>
+      </c>
+      <c r="P359" t="n">
+        <v>374.3</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>374.25</v>
+      </c>
+      <c r="R359" t="n">
+        <v>383.76</v>
+      </c>
+      <c r="S359" t="n">
+        <v>381.68</v>
+      </c>
+      <c r="T359" t="n">
+        <v>372.38</v>
+      </c>
+      <c r="U359" t="n">
+        <v>359.39</v>
+      </c>
+      <c r="V359" t="n">
+        <v>355.91</v>
+      </c>
+      <c r="W359" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27259,7 +27409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B359"/>
+  <dimension ref="A1:B361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30852,6 +31002,26 @@
       </c>
       <c r="B359" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -31020,28 +31190,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1262542862357675</v>
+        <v>-0.1273912370904365</v>
       </c>
       <c r="J2" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K2" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06414735016817785</v>
+        <v>0.06605092289835057</v>
       </c>
       <c r="M2" t="n">
-        <v>2.688730298627827</v>
+        <v>2.678453495223414</v>
       </c>
       <c r="N2" t="n">
-        <v>12.44863481445584</v>
+        <v>12.38417973147222</v>
       </c>
       <c r="O2" t="n">
-        <v>3.528262293885737</v>
+        <v>3.519116328209714</v>
       </c>
       <c r="P2" t="n">
-        <v>357.9144637189983</v>
+        <v>357.9262500890763</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31098,28 +31268,28 @@
         <v>0.0311</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0903432097602429</v>
+        <v>-0.08992052093790037</v>
       </c>
       <c r="J3" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K3" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03197110379188539</v>
+        <v>0.03210369363272114</v>
       </c>
       <c r="M3" t="n">
-        <v>2.833589945832175</v>
+        <v>2.819839568915053</v>
       </c>
       <c r="N3" t="n">
-        <v>13.22886045383022</v>
+        <v>13.1563460407779</v>
       </c>
       <c r="O3" t="n">
-        <v>3.637150045548055</v>
+        <v>3.627167771247686</v>
       </c>
       <c r="P3" t="n">
-        <v>352.5780254443654</v>
+        <v>352.5736414983423</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31176,28 +31346,28 @@
         <v>0.0361</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08735951139621911</v>
+        <v>0.08643824343545299</v>
       </c>
       <c r="J4" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K4" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02750515550856469</v>
+        <v>0.02730065466778275</v>
       </c>
       <c r="M4" t="n">
-        <v>2.980204355940839</v>
+        <v>2.967855696348356</v>
       </c>
       <c r="N4" t="n">
-        <v>14.44422707348618</v>
+        <v>14.36684004895401</v>
       </c>
       <c r="O4" t="n">
-        <v>3.800556153181555</v>
+        <v>3.790361466793636</v>
       </c>
       <c r="P4" t="n">
-        <v>354.8781420033571</v>
+        <v>354.8876929702952</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31254,28 +31424,28 @@
         <v>0.0411</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07665911850617667</v>
+        <v>0.07749870188574685</v>
       </c>
       <c r="J5" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K5" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01982462669120744</v>
+        <v>0.02052189785395564</v>
       </c>
       <c r="M5" t="n">
-        <v>3.142984566673069</v>
+        <v>3.129184741836158</v>
       </c>
       <c r="N5" t="n">
-        <v>15.55346378673102</v>
+        <v>15.47069751048427</v>
       </c>
       <c r="O5" t="n">
-        <v>3.943787999719435</v>
+        <v>3.933280756631069</v>
       </c>
       <c r="P5" t="n">
-        <v>345.3601043815324</v>
+        <v>345.3513976702196</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31332,28 +31502,28 @@
         <v>0.0456</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1444110547775819</v>
+        <v>0.1469308919805872</v>
       </c>
       <c r="J6" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K6" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08192469738294694</v>
+        <v>0.08547929804710863</v>
       </c>
       <c r="M6" t="n">
-        <v>2.846930288377239</v>
+        <v>2.84185485363809</v>
       </c>
       <c r="N6" t="n">
-        <v>12.51022297484358</v>
+        <v>12.46529765150859</v>
       </c>
       <c r="O6" t="n">
-        <v>3.536979357424012</v>
+        <v>3.530622841866375</v>
       </c>
       <c r="P6" t="n">
-        <v>343.2863956310568</v>
+        <v>343.2602732742944</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31410,28 +31580,28 @@
         <v>0.0468</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1460743698359996</v>
+        <v>0.1447599499475129</v>
       </c>
       <c r="J7" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K7" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09613264256650267</v>
+        <v>0.09569865543261713</v>
       </c>
       <c r="M7" t="n">
-        <v>2.740593022914085</v>
+        <v>2.730883035754266</v>
       </c>
       <c r="N7" t="n">
-        <v>10.73946324937727</v>
+        <v>10.68680827948046</v>
       </c>
       <c r="O7" t="n">
-        <v>3.277112028810927</v>
+        <v>3.269068411563218</v>
       </c>
       <c r="P7" t="n">
-        <v>355.0507416422857</v>
+        <v>355.064366618003</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31488,28 +31658,28 @@
         <v>0.0413</v>
       </c>
       <c r="I8" t="n">
-        <v>0.006500883822640979</v>
+        <v>-2.320442433759749e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K8" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001773312514063985</v>
+        <v>2.261324905106221e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>2.812755628825083</v>
+        <v>2.824772336139536</v>
       </c>
       <c r="N8" t="n">
-        <v>12.75508101940057</v>
+        <v>12.85058185944414</v>
       </c>
       <c r="O8" t="n">
-        <v>3.571425628429153</v>
+        <v>3.584770823838554</v>
       </c>
       <c r="P8" t="n">
-        <v>355.7199036613044</v>
+        <v>355.7875374180982</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31566,28 +31736,28 @@
         <v>0.0415</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03521261065632582</v>
+        <v>0.02827801260553002</v>
       </c>
       <c r="J9" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K9" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00467937806898322</v>
+        <v>0.003024239795671346</v>
       </c>
       <c r="M9" t="n">
-        <v>3.137625454667177</v>
+        <v>3.14530575088994</v>
       </c>
       <c r="N9" t="n">
-        <v>14.11796263252613</v>
+        <v>14.22688994483056</v>
       </c>
       <c r="O9" t="n">
-        <v>3.757387740508841</v>
+        <v>3.771854973992314</v>
       </c>
       <c r="P9" t="n">
-        <v>369.1602145671881</v>
+        <v>369.2321047700517</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31644,28 +31814,28 @@
         <v>0.0443</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07033612181837462</v>
+        <v>0.06506424190290616</v>
       </c>
       <c r="J10" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K10" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01490072438417189</v>
+        <v>0.01287393247567192</v>
       </c>
       <c r="M10" t="n">
-        <v>3.465855127095703</v>
+        <v>3.468209095754557</v>
       </c>
       <c r="N10" t="n">
-        <v>17.50774315458739</v>
+        <v>17.51821978808139</v>
       </c>
       <c r="O10" t="n">
-        <v>4.18422551430816</v>
+        <v>4.185477247349624</v>
       </c>
       <c r="P10" t="n">
-        <v>364.7207656040862</v>
+        <v>364.77541940056</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31722,28 +31892,28 @@
         <v>0.0429</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06316940446793967</v>
+        <v>0.06010097895788548</v>
       </c>
       <c r="J11" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K11" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01929614819081782</v>
+        <v>0.0176779126786305</v>
       </c>
       <c r="M11" t="n">
-        <v>2.632775313470153</v>
+        <v>2.631640619987276</v>
       </c>
       <c r="N11" t="n">
-        <v>10.85629240094982</v>
+        <v>10.83252864478628</v>
       </c>
       <c r="O11" t="n">
-        <v>3.294888829831716</v>
+        <v>3.291280699786373</v>
       </c>
       <c r="P11" t="n">
-        <v>354.72613602137</v>
+        <v>354.7579457029018</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31800,28 +31970,28 @@
         <v>0.0355</v>
       </c>
       <c r="I12" t="n">
-        <v>0.00618722810392335</v>
+        <v>0.0008779572309627204</v>
       </c>
       <c r="J12" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K12" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0001550386323281305</v>
+        <v>3.139146677377802e-06</v>
       </c>
       <c r="M12" t="n">
-        <v>2.899928922712407</v>
+        <v>2.911506458712508</v>
       </c>
       <c r="N12" t="n">
-        <v>13.21556393635571</v>
+        <v>13.25188252136659</v>
       </c>
       <c r="O12" t="n">
-        <v>3.635321710159324</v>
+        <v>3.640313519652749</v>
       </c>
       <c r="P12" t="n">
-        <v>357.2795479277617</v>
+        <v>357.3345884140329</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31878,28 +32048,28 @@
         <v>0.0256</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1465577727583039</v>
+        <v>-0.1442847437368236</v>
       </c>
       <c r="J13" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K13" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04633141133835483</v>
+        <v>0.0455222039459956</v>
       </c>
       <c r="M13" t="n">
-        <v>3.714728211683604</v>
+        <v>3.703648557169513</v>
       </c>
       <c r="N13" t="n">
-        <v>23.66684534946018</v>
+        <v>23.55739172735966</v>
       </c>
       <c r="O13" t="n">
-        <v>4.864858204455725</v>
+        <v>4.853595752363361</v>
       </c>
       <c r="P13" t="n">
-        <v>369.4106711926777</v>
+        <v>369.3871027667824</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31956,28 +32126,28 @@
         <v>0.0262</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.03186691197702633</v>
+        <v>-0.03042375213744678</v>
       </c>
       <c r="J14" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K14" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L14" t="n">
-        <v>0.003021257118345222</v>
+        <v>0.00279131419223333</v>
       </c>
       <c r="M14" t="n">
-        <v>3.395928921969675</v>
+        <v>3.384137457650063</v>
       </c>
       <c r="N14" t="n">
-        <v>17.93820095738229</v>
+        <v>17.84623906503608</v>
       </c>
       <c r="O14" t="n">
-        <v>4.235351338127959</v>
+        <v>4.224480922555584</v>
       </c>
       <c r="P14" t="n">
-        <v>367.9836592576624</v>
+        <v>367.9686970089523</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32034,28 +32204,28 @@
         <v>0.0255</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1233179887893545</v>
+        <v>-0.1225274135063867</v>
       </c>
       <c r="J15" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K15" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04177664341133236</v>
+        <v>0.04180385055593594</v>
       </c>
       <c r="M15" t="n">
-        <v>3.384931649332463</v>
+        <v>3.369752874701222</v>
       </c>
       <c r="N15" t="n">
-        <v>18.67182581042341</v>
+        <v>18.57156469790824</v>
       </c>
       <c r="O15" t="n">
-        <v>4.321090812563814</v>
+        <v>4.309473830748742</v>
       </c>
       <c r="P15" t="n">
-        <v>372.0174057637921</v>
+        <v>372.0092069058551</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32112,28 +32282,28 @@
         <v>0.0261</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1265157745175576</v>
+        <v>-0.1294427210527649</v>
       </c>
       <c r="J16" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K16" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L16" t="n">
-        <v>0.04141839298712813</v>
+        <v>0.04376818826327611</v>
       </c>
       <c r="M16" t="n">
-        <v>3.687076789944598</v>
+        <v>3.679792540001683</v>
       </c>
       <c r="N16" t="n">
-        <v>19.83014618618623</v>
+        <v>19.75621366671317</v>
       </c>
       <c r="O16" t="n">
-        <v>4.453105229633163</v>
+        <v>4.444796245803982</v>
       </c>
       <c r="P16" t="n">
-        <v>379.3433116214152</v>
+        <v>379.3736514012945</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32190,28 +32360,28 @@
         <v>0.0267</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1588497721624517</v>
+        <v>-0.1573494760503025</v>
       </c>
       <c r="J17" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K17" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L17" t="n">
-        <v>0.07376420708664311</v>
+        <v>0.07337267376250045</v>
       </c>
       <c r="M17" t="n">
-        <v>3.312038457628717</v>
+        <v>3.300418281695545</v>
       </c>
       <c r="N17" t="n">
-        <v>16.96093482331884</v>
+        <v>16.87505470221979</v>
       </c>
       <c r="O17" t="n">
-        <v>4.118365552415041</v>
+        <v>4.107925839425511</v>
       </c>
       <c r="P17" t="n">
-        <v>377.3435591183973</v>
+        <v>377.3280061108788</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32268,28 +32438,28 @@
         <v>0.0328</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.02942677514015625</v>
+        <v>-0.02769060278661512</v>
       </c>
       <c r="J18" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K18" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002963076306643164</v>
+        <v>0.002658785116617657</v>
       </c>
       <c r="M18" t="n">
-        <v>3.077896770910347</v>
+        <v>3.068368048740695</v>
       </c>
       <c r="N18" t="n">
-        <v>15.59748078008291</v>
+        <v>15.52276834497792</v>
       </c>
       <c r="O18" t="n">
-        <v>3.949364604601974</v>
+        <v>3.939894458609001</v>
       </c>
       <c r="P18" t="n">
-        <v>382.7282154331842</v>
+        <v>382.7102144649861</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32346,28 +32516,28 @@
         <v>0.033</v>
       </c>
       <c r="I19" t="n">
-        <v>0.002168822868394781</v>
+        <v>0.005031344638414662</v>
       </c>
       <c r="J19" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K19" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L19" t="n">
-        <v>1.266410838107745e-05</v>
+        <v>6.898179713277219e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.172760442633782</v>
+        <v>3.169037645894317</v>
       </c>
       <c r="N19" t="n">
-        <v>19.88239788791493</v>
+        <v>19.80375289256479</v>
       </c>
       <c r="O19" t="n">
-        <v>4.458968253746032</v>
+        <v>4.450140772218874</v>
       </c>
       <c r="P19" t="n">
-        <v>378.8987944598786</v>
+        <v>378.8691167450858</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32424,28 +32594,28 @@
         <v>0.036</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03403559398065421</v>
+        <v>0.03601202003920723</v>
       </c>
       <c r="J20" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K20" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L20" t="n">
-        <v>0.003250419417313521</v>
+        <v>0.003684519133595576</v>
       </c>
       <c r="M20" t="n">
-        <v>3.309098651766631</v>
+        <v>3.30070424546111</v>
       </c>
       <c r="N20" t="n">
-        <v>19.01577534156609</v>
+        <v>18.92582664350363</v>
       </c>
       <c r="O20" t="n">
-        <v>4.360708123867738</v>
+        <v>4.350382356012357</v>
       </c>
       <c r="P20" t="n">
-        <v>369.366413835353</v>
+        <v>369.345921660363</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32502,28 +32672,28 @@
         <v>0.0526</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1053401123477687</v>
+        <v>0.1040775263384799</v>
       </c>
       <c r="J21" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K21" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03935034353979139</v>
+        <v>0.03894206851616655</v>
       </c>
       <c r="M21" t="n">
-        <v>2.894047465254377</v>
+        <v>2.883129751880407</v>
       </c>
       <c r="N21" t="n">
-        <v>14.50122761958871</v>
+        <v>14.42740764648006</v>
       </c>
       <c r="O21" t="n">
-        <v>3.808047743869385</v>
+        <v>3.798342750000328</v>
       </c>
       <c r="P21" t="n">
-        <v>357.2433510682552</v>
+        <v>357.2564382040766</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32580,28 +32750,28 @@
         <v>0.0488</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0104897346655246</v>
+        <v>-0.01638645266065315</v>
       </c>
       <c r="J22" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K22" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0004238628832334834</v>
+        <v>0.001037775905199712</v>
       </c>
       <c r="M22" t="n">
-        <v>2.732332072991292</v>
+        <v>2.740847198331241</v>
       </c>
       <c r="N22" t="n">
-        <v>13.89057453635063</v>
+        <v>13.94951817067698</v>
       </c>
       <c r="O22" t="n">
-        <v>3.727006108976832</v>
+        <v>3.734905376402055</v>
       </c>
       <c r="P22" t="n">
-        <v>360.7249054138164</v>
+        <v>360.786034996747</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32639,7 +32809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W357"/>
+  <dimension ref="A1:W359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74411,6 +74581,240 @@
         </is>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:03+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>-39.19702368186381,177.92021095944705</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>-39.1976253629283,177.91975480097545</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>-39.19826478841221,177.91939832693788</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-39.1988385833703,177.91887741878858</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-39.199442105809695,177.91842569150597</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-39.20009456396676,177.91815417458977</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-39.20077245848658,177.91793256568434</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-39.20147494594916,177.91796262764373</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>-39.20216201295187,177.91781254550457</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>-39.20284161058463,177.91759008762807</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-39.203484307047646,177.9172598955681</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>-39.20416974623453,177.9170599448442</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>-39.20481252284268,177.91672429467883</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>-39.20546224106061,177.91641429157326</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>-39.206125989454165,177.9161481465645</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>-39.20678417440925,177.91585935695866</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>-39.20745995374429,177.91565036800537</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>-39.208111681414366,177.91533948080988</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>-39.20874592421721,177.91494432498806</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>-39.209371612141666,177.91451172424985</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>-39.21001841001801,177.91417299925388</t>
+        </is>
+      </c>
+      <c r="W358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:54:09+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>-39.197024428130476,177.9202129343176</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>-39.19762815162651,177.9197621808108</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>-39.19826470884856,177.91939811968786</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-39.19884280038298,177.91888762420285</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>-39.199440561307306,177.91842151731248</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>-39.20009598854401,177.91816157815362</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-39.200773276240156,177.9179419827735</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-39.20147551112451,177.91796929045466</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-39.20216214789463,177.91781415399132</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>-39.20284237815555,177.9175944851286</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>-39.20348581909146,177.91726521407293</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>-39.204174156982646,177.9170747269341</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>-39.20481346799217,177.91672766485354</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>-39.20546529695649,177.9164261382674</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>-39.206130357306,177.9161653997748</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>-39.20678340255744,177.91585627695713</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>-39.207461814859485,177.91565809589744</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>-39.20811328484714,177.9153463432113</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>-39.20874820007828,177.9149540652544</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>-39.209373829911186,177.91452100415424</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>-39.21002078081428,177.91418270221791</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0287/nzd0287.xlsx
+++ b/data/nzd0287/nzd0287.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W359"/>
+  <dimension ref="A1:W361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27393,6 +27393,156 @@
         <v>355.91</v>
       </c>
       <c r="W359" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>354.12</v>
+      </c>
+      <c r="C360" t="n">
+        <v>348.62</v>
+      </c>
+      <c r="D360" t="n">
+        <v>354.5</v>
+      </c>
+      <c r="E360" t="n">
+        <v>346.66</v>
+      </c>
+      <c r="F360" t="n">
+        <v>346.32</v>
+      </c>
+      <c r="G360" t="n">
+        <v>357.38</v>
+      </c>
+      <c r="H360" t="n">
+        <v>348.86</v>
+      </c>
+      <c r="I360" t="n">
+        <v>365.54</v>
+      </c>
+      <c r="J360" t="n">
+        <v>360.85</v>
+      </c>
+      <c r="K360" t="n">
+        <v>352.83</v>
+      </c>
+      <c r="L360" t="n">
+        <v>352.42</v>
+      </c>
+      <c r="M360" t="n">
+        <v>364.17</v>
+      </c>
+      <c r="N360" t="n">
+        <v>367.36</v>
+      </c>
+      <c r="O360" t="n">
+        <v>367.24</v>
+      </c>
+      <c r="P360" t="n">
+        <v>370.16</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>371</v>
+      </c>
+      <c r="R360" t="n">
+        <v>381.53</v>
+      </c>
+      <c r="S360" t="n">
+        <v>378.7</v>
+      </c>
+      <c r="T360" t="n">
+        <v>370.08</v>
+      </c>
+      <c r="U360" t="n">
+        <v>356.66</v>
+      </c>
+      <c r="V360" t="n">
+        <v>353.84</v>
+      </c>
+      <c r="W360" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>353.92</v>
+      </c>
+      <c r="C361" t="n">
+        <v>349.24</v>
+      </c>
+      <c r="D361" t="n">
+        <v>354.02</v>
+      </c>
+      <c r="E361" t="n">
+        <v>346.1</v>
+      </c>
+      <c r="F361" t="n">
+        <v>345.84</v>
+      </c>
+      <c r="G361" t="n">
+        <v>358.14</v>
+      </c>
+      <c r="H361" t="n">
+        <v>349.25</v>
+      </c>
+      <c r="I361" t="n">
+        <v>366.04</v>
+      </c>
+      <c r="J361" t="n">
+        <v>361.6</v>
+      </c>
+      <c r="K361" t="n">
+        <v>352.63</v>
+      </c>
+      <c r="L361" t="n">
+        <v>353.21</v>
+      </c>
+      <c r="M361" t="n">
+        <v>364.68</v>
+      </c>
+      <c r="N361" t="n">
+        <v>367.91</v>
+      </c>
+      <c r="O361" t="n">
+        <v>368.81</v>
+      </c>
+      <c r="P361" t="n">
+        <v>371.6</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>371.27</v>
+      </c>
+      <c r="R361" t="n">
+        <v>382.36</v>
+      </c>
+      <c r="S361" t="n">
+        <v>379.8</v>
+      </c>
+      <c r="T361" t="n">
+        <v>370.98</v>
+      </c>
+      <c r="U361" t="n">
+        <v>360.02</v>
+      </c>
+      <c r="V361" t="n">
+        <v>358.3</v>
+      </c>
+      <c r="W361" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27409,7 +27559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B361"/>
+  <dimension ref="A1:B363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31022,6 +31172,26 @@
       </c>
       <c r="B361" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>-0.2</v>
       </c>
     </row>
   </sheetData>
@@ -31190,28 +31360,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1273912370904365</v>
+        <v>-0.1279920356912004</v>
       </c>
       <c r="J2" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K2" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06605092289835057</v>
+        <v>0.06748213421493254</v>
       </c>
       <c r="M2" t="n">
-        <v>2.678453495223414</v>
+        <v>2.666068658544647</v>
       </c>
       <c r="N2" t="n">
-        <v>12.38417973147222</v>
+        <v>12.31685475091806</v>
       </c>
       <c r="O2" t="n">
-        <v>3.519116328209714</v>
+        <v>3.509537683359172</v>
       </c>
       <c r="P2" t="n">
-        <v>357.9262500890763</v>
+        <v>357.9325069581717</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31268,28 +31438,28 @@
         <v>0.0311</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08992052093790037</v>
+        <v>-0.09138754120512455</v>
       </c>
       <c r="J3" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K3" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03210369363272114</v>
+        <v>0.03354327903395693</v>
       </c>
       <c r="M3" t="n">
-        <v>2.819839568915053</v>
+        <v>2.810814096992743</v>
       </c>
       <c r="N3" t="n">
-        <v>13.1563460407779</v>
+        <v>13.09231531488581</v>
       </c>
       <c r="O3" t="n">
-        <v>3.627167771247686</v>
+        <v>3.618330459602302</v>
       </c>
       <c r="P3" t="n">
-        <v>352.5736414983423</v>
+        <v>352.5889107027389</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31346,28 +31516,28 @@
         <v>0.0361</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08643824343545299</v>
+        <v>0.08299411395572071</v>
       </c>
       <c r="J4" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K4" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02730065466778275</v>
+        <v>0.02547876660314585</v>
       </c>
       <c r="M4" t="n">
-        <v>2.967855696348356</v>
+        <v>2.967202006178707</v>
       </c>
       <c r="N4" t="n">
-        <v>14.36684004895401</v>
+        <v>14.33418701887221</v>
       </c>
       <c r="O4" t="n">
-        <v>3.790361466793636</v>
+        <v>3.786051639752449</v>
       </c>
       <c r="P4" t="n">
-        <v>354.8876929702952</v>
+        <v>354.9235560929841</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31424,28 +31594,28 @@
         <v>0.0411</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07749870188574685</v>
+        <v>0.07628218465452087</v>
       </c>
       <c r="J5" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K5" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02052189785395564</v>
+        <v>0.0201558576593357</v>
       </c>
       <c r="M5" t="n">
-        <v>3.129184741836158</v>
+        <v>3.117720300100329</v>
       </c>
       <c r="N5" t="n">
-        <v>15.47069751048427</v>
+        <v>15.3910247970902</v>
       </c>
       <c r="O5" t="n">
-        <v>3.933280756631069</v>
+        <v>3.923139660665957</v>
       </c>
       <c r="P5" t="n">
-        <v>345.3513976702196</v>
+        <v>345.364068148606</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31502,28 +31672,28 @@
         <v>0.0456</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1469308919805872</v>
+        <v>0.1456419911462911</v>
       </c>
       <c r="J6" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K6" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08547929804710863</v>
+        <v>0.08512846251872708</v>
       </c>
       <c r="M6" t="n">
-        <v>2.84185485363809</v>
+        <v>2.832561096677975</v>
       </c>
       <c r="N6" t="n">
-        <v>12.46529765150859</v>
+        <v>12.40292499617177</v>
       </c>
       <c r="O6" t="n">
-        <v>3.530622841866375</v>
+        <v>3.521778669390196</v>
       </c>
       <c r="P6" t="n">
-        <v>343.2602732742944</v>
+        <v>343.2736967682037</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31580,28 +31750,28 @@
         <v>0.0468</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1447599499475129</v>
+        <v>0.1434003388991051</v>
       </c>
       <c r="J7" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K7" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09569865543261713</v>
+        <v>0.09518457733098418</v>
       </c>
       <c r="M7" t="n">
-        <v>2.730883035754266</v>
+        <v>2.721571410195335</v>
       </c>
       <c r="N7" t="n">
-        <v>10.68680827948046</v>
+        <v>10.63553495789499</v>
       </c>
       <c r="O7" t="n">
-        <v>3.269068411563218</v>
+        <v>3.26121679099918</v>
       </c>
       <c r="P7" t="n">
-        <v>355.064366618003</v>
+        <v>355.0785165323324</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31658,28 +31828,28 @@
         <v>0.0413</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.320442433759749e-05</v>
+        <v>-0.007928866738994329</v>
       </c>
       <c r="J8" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K8" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L8" t="n">
-        <v>2.261324905106221e-09</v>
+        <v>0.000262513725409752</v>
       </c>
       <c r="M8" t="n">
-        <v>2.824772336139536</v>
+        <v>2.84254863768226</v>
       </c>
       <c r="N8" t="n">
-        <v>12.85058185944414</v>
+        <v>13.02632094261971</v>
       </c>
       <c r="O8" t="n">
-        <v>3.584770823838554</v>
+        <v>3.609199487783921</v>
       </c>
       <c r="P8" t="n">
-        <v>355.7875374180982</v>
+        <v>355.8698457320412</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31736,28 +31906,28 @@
         <v>0.0415</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02827801260553002</v>
+        <v>0.0233499818848343</v>
       </c>
       <c r="J9" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K9" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003024239795671346</v>
+        <v>0.002078254239511246</v>
       </c>
       <c r="M9" t="n">
-        <v>3.14530575088994</v>
+        <v>3.145463669415076</v>
       </c>
       <c r="N9" t="n">
-        <v>14.22688994483056</v>
+        <v>14.24414816501628</v>
       </c>
       <c r="O9" t="n">
-        <v>3.771854973992314</v>
+        <v>3.774142043566496</v>
       </c>
       <c r="P9" t="n">
-        <v>369.2321047700517</v>
+        <v>369.2834100739846</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31814,28 +31984,28 @@
         <v>0.0443</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06506424190290616</v>
+        <v>0.05885897962518214</v>
       </c>
       <c r="J10" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K10" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01287393247567192</v>
+        <v>0.0106118557171061</v>
       </c>
       <c r="M10" t="n">
-        <v>3.468209095754557</v>
+        <v>3.474735633976383</v>
       </c>
       <c r="N10" t="n">
-        <v>17.51821978808139</v>
+        <v>17.57382909134783</v>
       </c>
       <c r="O10" t="n">
-        <v>4.185477247349624</v>
+        <v>4.19211510950592</v>
       </c>
       <c r="P10" t="n">
-        <v>364.77541940056</v>
+        <v>364.8400208410742</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31892,28 +32062,28 @@
         <v>0.0429</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06010097895788548</v>
+        <v>0.05583604517630945</v>
       </c>
       <c r="J11" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K11" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0176779126786305</v>
+        <v>0.01540121334333444</v>
       </c>
       <c r="M11" t="n">
-        <v>2.631640619987276</v>
+        <v>2.635864314440998</v>
       </c>
       <c r="N11" t="n">
-        <v>10.83252864478628</v>
+        <v>10.84424284187254</v>
       </c>
       <c r="O11" t="n">
-        <v>3.291280699786373</v>
+        <v>3.293059799316213</v>
       </c>
       <c r="P11" t="n">
-        <v>354.7579457029018</v>
+        <v>354.8023525282488</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31970,28 +32140,28 @@
         <v>0.0355</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0008779572309627204</v>
+        <v>-0.004460150659673819</v>
       </c>
       <c r="J12" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K12" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L12" t="n">
-        <v>3.139146677377802e-06</v>
+        <v>8.142300530822322e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>2.911506458712508</v>
+        <v>2.923435792516089</v>
       </c>
       <c r="N12" t="n">
-        <v>13.25188252136659</v>
+        <v>13.29174932534084</v>
       </c>
       <c r="O12" t="n">
-        <v>3.640313519652749</v>
+        <v>3.645785145252095</v>
       </c>
       <c r="P12" t="n">
-        <v>357.3345884140329</v>
+        <v>357.3901609258984</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32048,28 +32218,28 @@
         <v>0.0256</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1442847437368236</v>
+        <v>-0.1455986249745648</v>
       </c>
       <c r="J13" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K13" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0455222039459956</v>
+        <v>0.04691076710762365</v>
       </c>
       <c r="M13" t="n">
-        <v>3.703648557169513</v>
+        <v>3.68973182935679</v>
       </c>
       <c r="N13" t="n">
-        <v>23.55739172735966</v>
+        <v>23.43371538025131</v>
       </c>
       <c r="O13" t="n">
-        <v>4.853595752363361</v>
+        <v>4.840838293131812</v>
       </c>
       <c r="P13" t="n">
-        <v>369.3871027667824</v>
+        <v>369.4007784149985</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32126,28 +32296,28 @@
         <v>0.0262</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.03042375213744678</v>
+        <v>-0.02986459057175497</v>
       </c>
       <c r="J14" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K14" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L14" t="n">
-        <v>0.00279131419223333</v>
+        <v>0.002726624584307391</v>
       </c>
       <c r="M14" t="n">
-        <v>3.384137457650063</v>
+        <v>3.368072441140264</v>
       </c>
       <c r="N14" t="n">
-        <v>17.84623906503608</v>
+        <v>17.74874231004803</v>
       </c>
       <c r="O14" t="n">
-        <v>4.224480922555584</v>
+        <v>4.212925623607427</v>
       </c>
       <c r="P14" t="n">
-        <v>367.9686970089523</v>
+        <v>367.962870831118</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32204,28 +32374,28 @@
         <v>0.0255</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1225274135063867</v>
+        <v>-0.1233698776195012</v>
       </c>
       <c r="J15" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K15" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04180385055593594</v>
+        <v>0.04290074480893113</v>
       </c>
       <c r="M15" t="n">
-        <v>3.369752874701222</v>
+        <v>3.355387657228589</v>
       </c>
       <c r="N15" t="n">
-        <v>18.57156469790824</v>
+        <v>18.47464020206328</v>
       </c>
       <c r="O15" t="n">
-        <v>4.309473830748742</v>
+        <v>4.298213605913889</v>
       </c>
       <c r="P15" t="n">
-        <v>372.0092069058551</v>
+        <v>372.0179659265023</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32282,28 +32452,28 @@
         <v>0.0261</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1294427210527649</v>
+        <v>-0.1353646704414969</v>
       </c>
       <c r="J16" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K16" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L16" t="n">
-        <v>0.04376818826327611</v>
+        <v>0.04796521719248603</v>
       </c>
       <c r="M16" t="n">
-        <v>3.679792540001683</v>
+        <v>3.686528047198523</v>
       </c>
       <c r="N16" t="n">
-        <v>19.75621366671317</v>
+        <v>19.78803346190466</v>
       </c>
       <c r="O16" t="n">
-        <v>4.444796245803982</v>
+        <v>4.448374249307792</v>
       </c>
       <c r="P16" t="n">
-        <v>379.3736514012945</v>
+        <v>379.4352974565144</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32360,28 +32530,28 @@
         <v>0.0267</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1573494760503025</v>
+        <v>-0.1596967614328095</v>
       </c>
       <c r="J17" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K17" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L17" t="n">
-        <v>0.07337267376250045</v>
+        <v>0.07627934336804965</v>
       </c>
       <c r="M17" t="n">
-        <v>3.300418281695545</v>
+        <v>3.293267090060962</v>
       </c>
       <c r="N17" t="n">
-        <v>16.87505470221979</v>
+        <v>16.8031808957942</v>
       </c>
       <c r="O17" t="n">
-        <v>4.107925839425511</v>
+        <v>4.099168317572992</v>
       </c>
       <c r="P17" t="n">
-        <v>377.3280061108788</v>
+        <v>377.3524431813046</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32438,28 +32608,28 @@
         <v>0.0328</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.02769060278661512</v>
+        <v>-0.02772140787732539</v>
       </c>
       <c r="J18" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K18" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002658785116617657</v>
+        <v>0.002701127266592551</v>
       </c>
       <c r="M18" t="n">
-        <v>3.068368048740695</v>
+        <v>3.053622300106404</v>
       </c>
       <c r="N18" t="n">
-        <v>15.52276834497792</v>
+        <v>15.43748050341764</v>
       </c>
       <c r="O18" t="n">
-        <v>3.939894458609001</v>
+        <v>3.929055930298988</v>
       </c>
       <c r="P18" t="n">
-        <v>382.7102144649861</v>
+        <v>382.7105286520738</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32516,28 +32686,28 @@
         <v>0.033</v>
       </c>
       <c r="I19" t="n">
-        <v>0.005031344638414662</v>
+        <v>0.005327012953637028</v>
       </c>
       <c r="J19" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K19" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L19" t="n">
-        <v>6.898179713277219e-05</v>
+        <v>7.838386651048967e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.169037645894317</v>
+        <v>3.154554303912423</v>
       </c>
       <c r="N19" t="n">
-        <v>19.80375289256479</v>
+        <v>19.695742394329</v>
       </c>
       <c r="O19" t="n">
-        <v>4.450140772218874</v>
+        <v>4.437988552748756</v>
       </c>
       <c r="P19" t="n">
-        <v>378.8691167450858</v>
+        <v>378.8660296361127</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32594,28 +32764,28 @@
         <v>0.036</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03601202003920723</v>
+        <v>0.03627823777064606</v>
       </c>
       <c r="J20" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K20" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L20" t="n">
-        <v>0.003684519133595576</v>
+        <v>0.003790021842603464</v>
       </c>
       <c r="M20" t="n">
-        <v>3.30070424546111</v>
+        <v>3.284943674031056</v>
       </c>
       <c r="N20" t="n">
-        <v>18.92582664350363</v>
+        <v>18.82205834884395</v>
       </c>
       <c r="O20" t="n">
-        <v>4.350382356012357</v>
+        <v>4.338439621435794</v>
       </c>
       <c r="P20" t="n">
-        <v>369.345921660363</v>
+        <v>369.3431428246969</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32672,28 +32842,28 @@
         <v>0.0526</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1040775263384799</v>
+        <v>0.1021005851590974</v>
       </c>
       <c r="J21" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K21" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03894206851616655</v>
+        <v>0.03794985841994303</v>
       </c>
       <c r="M21" t="n">
-        <v>2.883129751880407</v>
+        <v>2.875418240241728</v>
       </c>
       <c r="N21" t="n">
-        <v>14.42740764648006</v>
+        <v>14.3783676859011</v>
       </c>
       <c r="O21" t="n">
-        <v>3.798342750000328</v>
+        <v>3.791881813282305</v>
       </c>
       <c r="P21" t="n">
-        <v>357.2564382040766</v>
+        <v>357.2769949552115</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32750,28 +32920,28 @@
         <v>0.0488</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.01638645266065315</v>
+        <v>-0.02140644548412618</v>
       </c>
       <c r="J22" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K22" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L22" t="n">
-        <v>0.001037775905199712</v>
+        <v>0.001777730952313927</v>
       </c>
       <c r="M22" t="n">
-        <v>2.740847198331241</v>
+        <v>2.74717175317102</v>
       </c>
       <c r="N22" t="n">
-        <v>13.94951817067698</v>
+        <v>13.99960923838593</v>
       </c>
       <c r="O22" t="n">
-        <v>3.734905376402055</v>
+        <v>3.741605168692434</v>
       </c>
       <c r="P22" t="n">
-        <v>360.786034996747</v>
+        <v>360.8382662198915</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32809,7 +32979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W359"/>
+  <dimension ref="A1:W361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74815,6 +74985,240 @@
         </is>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>-39.19702607777248,177.92021729982093</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>-39.197619235645945,177.91973858612795</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>-39.19825711051891,177.91937832731134</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-39.19883461937749,177.91886782570026</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-39.19943005868677,177.91839313280127</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-39.20009432653718,177.9181529406625</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-39.20077134155362,177.91791970331886</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-39.20147648556384,177.91798077805987</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-39.20216083702102,177.91779852869166</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>-39.20284005576095,177.9175811798708</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>-39.2034833813064,177.91725663934076</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>-39.20416143985667,177.9170321070445</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>-39.20480996179191,177.91671516259288</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>-39.205457628919085,177.91639641184216</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>-39.206118839525246,177.91611990405238</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>-39.20677444355696,177.91582052694397</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>-39.207455885876385,177.9156334770425</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>-39.208105578021225,177.91531335941335</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>-39.20874225180322,177.91492860774125</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>-39.209366622157454,177.91449084446697</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>-39.210015204053526,177.91415987820116</t>
+        </is>
+      </c>
+      <c r="W360" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>-39.19702529222869,177.92021522100978</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>-39.1976216708482,177.9197450304901</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>-39.19825520099045,177.91937335331158</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-39.19883225784944,177.91886211066938</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-39.199428205282366,177.9183881237707</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-39.200095966959495,177.9181614659784</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-39.2007717304858,177.91792418217824</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-39.20147697278308,177.91798652186256</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-39.20216155992952,177.91780714558482</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-39.20283966213459,177.91757892474246</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-39.20348581909146,177.91726521407293</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>-39.20416308181564,177.91703760986488</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>-39.20481163867048,177.91672114193477</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>-39.205462071288586,177.91641363342362</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>-39.206122845711995,177.91613572864998</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>-39.20677518784359,177.91582349694477</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>-39.20745809262859,177.91564264011365</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>-39.20810842282389,177.91532553464003</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>-39.208744579389815,177.9149385693764</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>-39.2093754932378,177.91452796408282</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>-39.21002721967712,177.91420905458912</t>
+        </is>
+      </c>
+      <c r="W361" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0287/nzd0287.xlsx
+++ b/data/nzd0287/nzd0287.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W361"/>
+  <dimension ref="A1:W365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27543,6 +27543,306 @@
         <v>358.3</v>
       </c>
       <c r="W361" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>354.33</v>
+      </c>
+      <c r="C362" t="n">
+        <v>350.58</v>
+      </c>
+      <c r="D362" t="n">
+        <v>355.31</v>
+      </c>
+      <c r="E362" t="n">
+        <v>347.43</v>
+      </c>
+      <c r="F362" t="n">
+        <v>346.93</v>
+      </c>
+      <c r="G362" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="H362" t="n">
+        <v>350.84</v>
+      </c>
+      <c r="I362" t="n">
+        <v>366.05</v>
+      </c>
+      <c r="J362" t="n">
+        <v>362.79</v>
+      </c>
+      <c r="K362" t="n">
+        <v>353.23</v>
+      </c>
+      <c r="L362" t="n">
+        <v>354.01</v>
+      </c>
+      <c r="M362" t="n">
+        <v>366.86</v>
+      </c>
+      <c r="N362" t="n">
+        <v>368.96</v>
+      </c>
+      <c r="O362" t="n">
+        <v>370.64</v>
+      </c>
+      <c r="P362" t="n">
+        <v>373.98</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>373.02</v>
+      </c>
+      <c r="R362" t="n">
+        <v>382.87</v>
+      </c>
+      <c r="S362" t="n">
+        <v>380.34</v>
+      </c>
+      <c r="T362" t="n">
+        <v>371.98</v>
+      </c>
+      <c r="U362" t="n">
+        <v>360.14</v>
+      </c>
+      <c r="V362" t="n">
+        <v>358.44</v>
+      </c>
+      <c r="W362" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:35+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>353.99</v>
+      </c>
+      <c r="C363" t="n">
+        <v>349.84</v>
+      </c>
+      <c r="D363" t="n">
+        <v>355.14</v>
+      </c>
+      <c r="E363" t="n">
+        <v>346.99</v>
+      </c>
+      <c r="F363" t="n">
+        <v>346.01</v>
+      </c>
+      <c r="G363" t="n">
+        <v>358.67</v>
+      </c>
+      <c r="H363" t="n">
+        <v>350.45</v>
+      </c>
+      <c r="I363" t="n">
+        <v>366.94</v>
+      </c>
+      <c r="J363" t="n">
+        <v>363.07</v>
+      </c>
+      <c r="K363" t="n">
+        <v>353.92</v>
+      </c>
+      <c r="L363" t="n">
+        <v>354.35</v>
+      </c>
+      <c r="M363" t="n">
+        <v>365.82</v>
+      </c>
+      <c r="N363" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="O363" t="n">
+        <v>370.09</v>
+      </c>
+      <c r="P363" t="n">
+        <v>373.42</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>373.31</v>
+      </c>
+      <c r="R363" t="n">
+        <v>381.51</v>
+      </c>
+      <c r="S363" t="n">
+        <v>379.42</v>
+      </c>
+      <c r="T363" t="n">
+        <v>370.21</v>
+      </c>
+      <c r="U363" t="n">
+        <v>359.49</v>
+      </c>
+      <c r="V363" t="n">
+        <v>357</v>
+      </c>
+      <c r="W363" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:53:10+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>353.69</v>
+      </c>
+      <c r="C364" t="n">
+        <v>350.12</v>
+      </c>
+      <c r="D364" t="n">
+        <v>356.2</v>
+      </c>
+      <c r="E364" t="n">
+        <v>347.93</v>
+      </c>
+      <c r="F364" t="n">
+        <v>346.85</v>
+      </c>
+      <c r="G364" t="n">
+        <v>359.23</v>
+      </c>
+      <c r="H364" t="n">
+        <v>351.87</v>
+      </c>
+      <c r="I364" t="n">
+        <v>367.06</v>
+      </c>
+      <c r="J364" t="n">
+        <v>363.86</v>
+      </c>
+      <c r="K364" t="n">
+        <v>354.75</v>
+      </c>
+      <c r="L364" t="n">
+        <v>354.93</v>
+      </c>
+      <c r="M364" t="n">
+        <v>367.46</v>
+      </c>
+      <c r="N364" t="n">
+        <v>368.85</v>
+      </c>
+      <c r="O364" t="n">
+        <v>370.77</v>
+      </c>
+      <c r="P364" t="n">
+        <v>375.76</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>373.24</v>
+      </c>
+      <c r="R364" t="n">
+        <v>382.04</v>
+      </c>
+      <c r="S364" t="n">
+        <v>380.1</v>
+      </c>
+      <c r="T364" t="n">
+        <v>370.84</v>
+      </c>
+      <c r="U364" t="n">
+        <v>360.17</v>
+      </c>
+      <c r="V364" t="n">
+        <v>357.51</v>
+      </c>
+      <c r="W364" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:53:22+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>352.7</v>
+      </c>
+      <c r="C365" t="n">
+        <v>349.24</v>
+      </c>
+      <c r="D365" t="n">
+        <v>355.27</v>
+      </c>
+      <c r="E365" t="n">
+        <v>347.34</v>
+      </c>
+      <c r="F365" t="n">
+        <v>346.19</v>
+      </c>
+      <c r="G365" t="n">
+        <v>358.78</v>
+      </c>
+      <c r="H365" t="n">
+        <v>352.2</v>
+      </c>
+      <c r="I365" t="n">
+        <v>367.11</v>
+      </c>
+      <c r="J365" t="n">
+        <v>363.43</v>
+      </c>
+      <c r="K365" t="n">
+        <v>354.87</v>
+      </c>
+      <c r="L365" t="n">
+        <v>353.96</v>
+      </c>
+      <c r="M365" t="n">
+        <v>365.94</v>
+      </c>
+      <c r="N365" t="n">
+        <v>367.25</v>
+      </c>
+      <c r="O365" t="n">
+        <v>369.37</v>
+      </c>
+      <c r="P365" t="n">
+        <v>374.36</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>371.69</v>
+      </c>
+      <c r="R365" t="n">
+        <v>380</v>
+      </c>
+      <c r="S365" t="n">
+        <v>378.43</v>
+      </c>
+      <c r="T365" t="n">
+        <v>369.21</v>
+      </c>
+      <c r="U365" t="n">
+        <v>358.43</v>
+      </c>
+      <c r="V365" t="n">
+        <v>355.9</v>
+      </c>
+      <c r="W365" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27559,7 +27859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B363"/>
+  <dimension ref="A1:B367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31192,6 +31492,46 @@
       </c>
       <c r="B363" t="n">
         <v>-0.2</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>-0.59</v>
       </c>
     </row>
   </sheetData>
@@ -31360,28 +31700,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1279920356912004</v>
+        <v>-0.1298892904355373</v>
       </c>
       <c r="J2" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K2" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06748213421493254</v>
+        <v>0.07104457114066365</v>
       </c>
       <c r="M2" t="n">
-        <v>2.666068658544647</v>
+        <v>2.644575309159401</v>
       </c>
       <c r="N2" t="n">
-        <v>12.31685475091806</v>
+        <v>12.1928364556684</v>
       </c>
       <c r="O2" t="n">
-        <v>3.509537683359172</v>
+        <v>3.491824230351293</v>
       </c>
       <c r="P2" t="n">
-        <v>357.9325069581717</v>
+        <v>357.9523420037415</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31438,28 +31778,28 @@
         <v>0.0311</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09138754120512455</v>
+        <v>-0.0918507129617548</v>
       </c>
       <c r="J3" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K3" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03354327903395693</v>
+        <v>0.03475207797541602</v>
       </c>
       <c r="M3" t="n">
-        <v>2.810814096992743</v>
+        <v>2.784384262547047</v>
       </c>
       <c r="N3" t="n">
-        <v>13.09231531488581</v>
+        <v>12.9514156252673</v>
       </c>
       <c r="O3" t="n">
-        <v>3.618330459602302</v>
+        <v>3.598807528233109</v>
       </c>
       <c r="P3" t="n">
-        <v>352.5889107027389</v>
+        <v>352.593759367065</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31516,28 +31856,28 @@
         <v>0.0361</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08299411395572071</v>
+        <v>0.07920170084771239</v>
       </c>
       <c r="J4" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K4" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02547876660314585</v>
+        <v>0.02382112309351181</v>
       </c>
       <c r="M4" t="n">
-        <v>2.967202006178707</v>
+        <v>2.951821239408758</v>
       </c>
       <c r="N4" t="n">
-        <v>14.33418701887221</v>
+        <v>14.20791233139536</v>
       </c>
       <c r="O4" t="n">
-        <v>3.786051639752449</v>
+        <v>3.769338447446097</v>
       </c>
       <c r="P4" t="n">
-        <v>354.9235560929841</v>
+        <v>354.9631747362657</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31594,28 +31934,28 @@
         <v>0.0411</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07628218465452087</v>
+        <v>0.0763264068761066</v>
       </c>
       <c r="J5" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K5" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0201558576593357</v>
+        <v>0.02071327996820183</v>
       </c>
       <c r="M5" t="n">
-        <v>3.117720300100329</v>
+        <v>3.08632932483837</v>
       </c>
       <c r="N5" t="n">
-        <v>15.3910247970902</v>
+        <v>15.22315628173904</v>
       </c>
       <c r="O5" t="n">
-        <v>3.923139660665957</v>
+        <v>3.901686338205448</v>
       </c>
       <c r="P5" t="n">
-        <v>345.364068148606</v>
+        <v>345.3636044477457</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31672,28 +32012,28 @@
         <v>0.0456</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1456419911462911</v>
+        <v>0.1441093434804143</v>
       </c>
       <c r="J6" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K6" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08512846251872708</v>
+        <v>0.08552485295330281</v>
       </c>
       <c r="M6" t="n">
-        <v>2.832561096677975</v>
+        <v>2.809064819153122</v>
       </c>
       <c r="N6" t="n">
-        <v>12.40292499617177</v>
+        <v>12.27320335216897</v>
       </c>
       <c r="O6" t="n">
-        <v>3.521778669390196</v>
+        <v>3.50331319641407</v>
       </c>
       <c r="P6" t="n">
-        <v>343.2736967682037</v>
+        <v>343.2897127434103</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31750,28 +32090,28 @@
         <v>0.0468</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1434003388991051</v>
+        <v>0.1437053280519919</v>
       </c>
       <c r="J7" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K7" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09518457733098418</v>
+        <v>0.09787796337000843</v>
       </c>
       <c r="M7" t="n">
-        <v>2.721571410195335</v>
+        <v>2.695323396870535</v>
       </c>
       <c r="N7" t="n">
-        <v>10.63553495789499</v>
+        <v>10.52010775804074</v>
       </c>
       <c r="O7" t="n">
-        <v>3.26121679099918</v>
+        <v>3.243471559616447</v>
       </c>
       <c r="P7" t="n">
-        <v>355.0785165323324</v>
+        <v>355.0753344558785</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31828,28 +32168,28 @@
         <v>0.0413</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.007928866738994329</v>
+        <v>-0.01776806465976578</v>
       </c>
       <c r="J8" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K8" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L8" t="n">
-        <v>0.000262513725409752</v>
+        <v>0.001331633600568316</v>
       </c>
       <c r="M8" t="n">
-        <v>2.84254863768226</v>
+        <v>2.853000600561851</v>
       </c>
       <c r="N8" t="n">
-        <v>13.02632094261971</v>
+        <v>13.08611945126077</v>
       </c>
       <c r="O8" t="n">
-        <v>3.609199487783921</v>
+        <v>3.617474181146394</v>
       </c>
       <c r="P8" t="n">
-        <v>355.8698457320412</v>
+        <v>355.9726258987031</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31906,28 +32246,28 @@
         <v>0.0415</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0233499818848343</v>
+        <v>0.01624220976311418</v>
       </c>
       <c r="J9" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K9" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002078254239511246</v>
+        <v>0.001026303442932641</v>
       </c>
       <c r="M9" t="n">
-        <v>3.145463669415076</v>
+        <v>3.136723755181772</v>
       </c>
       <c r="N9" t="n">
-        <v>14.24414816501628</v>
+        <v>14.19262007201148</v>
       </c>
       <c r="O9" t="n">
-        <v>3.774142043566496</v>
+        <v>3.767309394250952</v>
       </c>
       <c r="P9" t="n">
-        <v>369.2834100739846</v>
+        <v>369.3576595562458</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31984,28 +32324,28 @@
         <v>0.0443</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05885897962518214</v>
+        <v>0.05173487850716262</v>
       </c>
       <c r="J10" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K10" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0106118557171061</v>
+        <v>0.008389093364737477</v>
       </c>
       <c r="M10" t="n">
-        <v>3.474735633976383</v>
+        <v>3.466776362665883</v>
       </c>
       <c r="N10" t="n">
-        <v>17.57382909134783</v>
+        <v>17.48586873929867</v>
       </c>
       <c r="O10" t="n">
-        <v>4.19211510950592</v>
+        <v>4.181610782856132</v>
       </c>
       <c r="P10" t="n">
-        <v>364.8400208410742</v>
+        <v>364.9144425363586</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32062,28 +32402,28 @@
         <v>0.0429</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05583604517630945</v>
+        <v>0.05104313410564538</v>
       </c>
       <c r="J11" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K11" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01540121334333444</v>
+        <v>0.01318603555485554</v>
       </c>
       <c r="M11" t="n">
-        <v>2.635864314440998</v>
+        <v>2.628141402619554</v>
       </c>
       <c r="N11" t="n">
-        <v>10.84424284187254</v>
+        <v>10.77679916181409</v>
       </c>
       <c r="O11" t="n">
-        <v>3.293059799316213</v>
+        <v>3.282803552120365</v>
       </c>
       <c r="P11" t="n">
-        <v>354.8023525282488</v>
+        <v>354.8524111679262</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32140,28 +32480,28 @@
         <v>0.0355</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.004460150659673819</v>
+        <v>-0.01121034106654994</v>
       </c>
       <c r="J12" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K12" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L12" t="n">
-        <v>8.142300530822322e-05</v>
+        <v>0.0005243376243279085</v>
       </c>
       <c r="M12" t="n">
-        <v>2.923435792516089</v>
+        <v>2.927383875280279</v>
       </c>
       <c r="N12" t="n">
-        <v>13.29174932534084</v>
+        <v>13.24015084072968</v>
       </c>
       <c r="O12" t="n">
-        <v>3.645785145252095</v>
+        <v>3.638701807063843</v>
       </c>
       <c r="P12" t="n">
-        <v>357.3901609258984</v>
+        <v>357.4606821277745</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32218,28 +32558,28 @@
         <v>0.0256</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1455986249745648</v>
+        <v>-0.1432936417322727</v>
       </c>
       <c r="J13" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K13" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04691076710762365</v>
+        <v>0.04665102803899934</v>
       </c>
       <c r="M13" t="n">
-        <v>3.68973182935679</v>
+        <v>3.659145635887181</v>
       </c>
       <c r="N13" t="n">
-        <v>23.43371538025131</v>
+        <v>23.19202145508265</v>
       </c>
       <c r="O13" t="n">
-        <v>4.840838293131812</v>
+        <v>4.815809532683227</v>
       </c>
       <c r="P13" t="n">
-        <v>369.4007784149985</v>
+        <v>369.3767000111043</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32296,28 +32636,28 @@
         <v>0.0262</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.02986459057175497</v>
+        <v>-0.02705868633079946</v>
       </c>
       <c r="J14" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K14" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002726624584307391</v>
+        <v>0.002297296009601379</v>
       </c>
       <c r="M14" t="n">
-        <v>3.368072441140264</v>
+        <v>3.344567022181983</v>
       </c>
       <c r="N14" t="n">
-        <v>17.74874231004803</v>
+        <v>17.57485244135949</v>
       </c>
       <c r="O14" t="n">
-        <v>4.212925623607427</v>
+        <v>4.192237164254843</v>
       </c>
       <c r="P14" t="n">
-        <v>367.962870831118</v>
+        <v>367.9335688987976</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32374,28 +32714,28 @@
         <v>0.0255</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1233698776195012</v>
+        <v>-0.1199545282834307</v>
       </c>
       <c r="J15" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K15" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04290074480893113</v>
+        <v>0.04165140135552448</v>
       </c>
       <c r="M15" t="n">
-        <v>3.355387657228589</v>
+        <v>3.334597412846048</v>
       </c>
       <c r="N15" t="n">
-        <v>18.47464020206328</v>
+        <v>18.29874346281783</v>
       </c>
       <c r="O15" t="n">
-        <v>4.298213605913889</v>
+        <v>4.277703059215054</v>
       </c>
       <c r="P15" t="n">
-        <v>372.0179659265023</v>
+        <v>371.9822923717325</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32452,28 +32792,28 @@
         <v>0.0261</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1353646704414969</v>
+        <v>-0.1386381910571617</v>
       </c>
       <c r="J16" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K16" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L16" t="n">
-        <v>0.04796521719248603</v>
+        <v>0.05141226222950146</v>
       </c>
       <c r="M16" t="n">
-        <v>3.686528047198523</v>
+        <v>3.660983237340592</v>
       </c>
       <c r="N16" t="n">
-        <v>19.78803346190466</v>
+        <v>19.6006574268425</v>
       </c>
       <c r="O16" t="n">
-        <v>4.448374249307792</v>
+        <v>4.427262972406598</v>
       </c>
       <c r="P16" t="n">
-        <v>379.4352974565144</v>
+        <v>379.4694881902464</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32530,28 +32870,28 @@
         <v>0.0267</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1596967614328095</v>
+        <v>-0.1603084812978841</v>
       </c>
       <c r="J17" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K17" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L17" t="n">
-        <v>0.07627934336804965</v>
+        <v>0.07871610726520561</v>
       </c>
       <c r="M17" t="n">
-        <v>3.293267090060962</v>
+        <v>3.262173624904585</v>
       </c>
       <c r="N17" t="n">
-        <v>16.8031808957942</v>
+        <v>16.62405430022687</v>
       </c>
       <c r="O17" t="n">
-        <v>4.099168317572992</v>
+        <v>4.077260636778923</v>
       </c>
       <c r="P17" t="n">
-        <v>377.3524431813046</v>
+        <v>377.3588447193638</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32608,28 +32948,28 @@
         <v>0.0328</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.02772140787732539</v>
+        <v>-0.02855669707474035</v>
       </c>
       <c r="J18" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K18" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002701127266592551</v>
+        <v>0.002940845556233418</v>
       </c>
       <c r="M18" t="n">
-        <v>3.053622300106404</v>
+        <v>3.029657121662723</v>
       </c>
       <c r="N18" t="n">
-        <v>15.43748050341764</v>
+        <v>15.28124494078871</v>
       </c>
       <c r="O18" t="n">
-        <v>3.929055930298988</v>
+        <v>3.909123295674966</v>
       </c>
       <c r="P18" t="n">
-        <v>382.7105286520738</v>
+        <v>382.7192764672059</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32686,28 +33026,28 @@
         <v>0.033</v>
       </c>
       <c r="I19" t="n">
-        <v>0.005327012953637028</v>
+        <v>0.006616260978774491</v>
       </c>
       <c r="J19" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K19" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L19" t="n">
-        <v>7.838386651048967e-05</v>
+        <v>0.0001241314555118223</v>
       </c>
       <c r="M19" t="n">
-        <v>3.154554303912423</v>
+        <v>3.129516134328927</v>
       </c>
       <c r="N19" t="n">
-        <v>19.695742394329</v>
+        <v>19.48873159433149</v>
       </c>
       <c r="O19" t="n">
-        <v>4.437988552748756</v>
+        <v>4.414604353091168</v>
       </c>
       <c r="P19" t="n">
-        <v>378.8660296361127</v>
+        <v>378.8525735003702</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32764,28 +33104,28 @@
         <v>0.036</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03627823777064606</v>
+        <v>0.0368366224615093</v>
       </c>
       <c r="J20" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K20" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L20" t="n">
-        <v>0.003790021842603464</v>
+        <v>0.00401020703365107</v>
       </c>
       <c r="M20" t="n">
-        <v>3.284943674031056</v>
+        <v>3.258400870270631</v>
       </c>
       <c r="N20" t="n">
-        <v>18.82205834884395</v>
+        <v>18.62695130483669</v>
       </c>
       <c r="O20" t="n">
-        <v>4.338439621435794</v>
+        <v>4.315895191595446</v>
       </c>
       <c r="P20" t="n">
-        <v>369.3431428246969</v>
+        <v>369.3373292670753</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32842,28 +33182,28 @@
         <v>0.0526</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1021005851590974</v>
+        <v>0.1010757625258903</v>
       </c>
       <c r="J21" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K21" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03794985841994303</v>
+        <v>0.03817170854705976</v>
       </c>
       <c r="M21" t="n">
-        <v>2.875418240241728</v>
+        <v>2.849919928016704</v>
       </c>
       <c r="N21" t="n">
-        <v>14.3783676859011</v>
+        <v>14.22800734619551</v>
       </c>
       <c r="O21" t="n">
-        <v>3.791881813282305</v>
+        <v>3.772003094669397</v>
       </c>
       <c r="P21" t="n">
-        <v>357.2769949552115</v>
+        <v>357.2877135007384</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32920,28 +33260,28 @@
         <v>0.0488</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.02140644548412618</v>
+        <v>-0.028372380391347</v>
       </c>
       <c r="J22" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K22" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L22" t="n">
-        <v>0.001777730952313927</v>
+        <v>0.003178438185615917</v>
       </c>
       <c r="M22" t="n">
-        <v>2.74717175317102</v>
+        <v>2.748672314663272</v>
       </c>
       <c r="N22" t="n">
-        <v>13.99960923838593</v>
+        <v>13.95369677827312</v>
       </c>
       <c r="O22" t="n">
-        <v>3.741605168692434</v>
+        <v>3.735464733908369</v>
       </c>
       <c r="P22" t="n">
-        <v>360.8382662198915</v>
+        <v>360.9110611284203</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32979,7 +33319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W361"/>
+  <dimension ref="A1:W365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75219,6 +75559,474 @@
         </is>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>-39.1970269025934,177.92021948257272</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>-39.197626934025934,177.9197589586291</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>-39.19826033284764,177.9193867209365</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-39.198837866478044,177.9188756838683</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>-39.19943241405453,177.91839949844461</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-39.20009890245045,177.91817672180764</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-39.20077331613056,177.9179424421437</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-39.20147698252745,177.91798663673862</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>-39.202162706943014,177.91782081772217</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>-39.20284084301354,177.91758569012762</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>-39.20348828773386,177.9172738973466</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>-39.20417010038226,177.91706113172725</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>-39.20481483998319,177.91673255704282</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>-39.20546724933373,177.91643370698915</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>-39.206129467043425,177.91616188319674</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>-39.206780011921694,177.9158427469512</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>-39.20745944858438,177.91564827043473</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>-39.20810981936288,177.91533151156983</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>-39.208747165596094,177.91494963786056</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>-39.20937581006188,177.91452928978353</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>-39.210027596848796,177.9142105982428</t>
+        </is>
+      </c>
+      <c r="W362" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:35+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>-39.197025567169014,177.9202159485937</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>-39.19762402749517,177.91975126697002</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>-39.19825965655647,177.91938495931137</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-39.198836010992075,177.91887119348647</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>-39.19942886169645,177.91838989780234</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-39.20009711093783,177.91816741126465</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-39.20077292719908,177.9179379632842</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-39.20147784977696,177.91799686070755</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>-39.20216297682831,177.9178240346957</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>-39.20284220102382,177.91759347032078</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>-39.20348933690667,177.91727758773806</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>-39.204166752075885,177.9170499102878</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>-39.204813559458245,177.91672799099948</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>-39.20546569309104,177.91642767395007</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>-39.20612790908366,177.91615572918533</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>-39.20678081134003,177.9158459369525</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>-39.207455832701626,177.9156332562456</t>
+        </is>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>-39.208107440074016,177.91532132865254</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>-39.208742588010224,177.91493004664406</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>-39.20937409393131,177.91452210890478</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>-39.21002371736757,177.91419472066283</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:53:10+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>-39.1970243888533,177.92021283037704</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>-39.197625127263635,177.91975417732743</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>-39.19826387343029,177.91939594356248</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>-39.1988399749846,177.91888078657516</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>-39.19943210515385,177.91839866360615</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>-39.200098319669316,177.91817369307677</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>-39.20077434330766,177.91795427092666</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>-39.20147796670942,177.91799823922022</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>-39.202163738289904,177.91783311115682</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>-39.20284383457169,177.9176028291042</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>-39.20349112667177,177.91728388311193</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>-39.204172032096935,177.9170676056351</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>-39.204814504607626,177.9167313611743</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>-39.20546761717286,177.91643513298027</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>-39.20613441912759,177.91618144416313</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>-39.206780618376996,177.91584516695218</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>-39.20745724183265,177.91563910736323</t>
+        </is>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>-39.20810919867892,177.91532885515656</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>-39.20874421732085,177.91493701978865</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>-39.20937588926789,177.91452962120874</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>-39.210025091350765,177.9142003439722</t>
+        </is>
+      </c>
+      <c r="W364" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:53:22+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>-39.197020500410744,177.9202025402627</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>-39.1976216708482,177.9197450304901</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>-39.198260173720314,177.91938630643645</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-39.19883748694684,177.91887476538108</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>-39.199429556723096,177.9183917761888</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>-39.20009734836727,177.91816864519203</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>-39.200774672402986,177.91795806073097</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>-39.20147801543127,177.9179988136005</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>-39.202163323823555,177.91782817080454</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>-39.202844070747226,177.91760418218135</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>-39.203488133443734,177.91727335464196</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>-39.20416713841898,177.91705120506924</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>-39.20480962641615,177.9167139667245</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>-39.205463655827394,177.9164197761538</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>-39.206130524230225,177.9161660591332</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>-39.20677634562265,177.9158281169461</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>-39.2074518180059,177.91561658608134</t>
+        </is>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>-39.208104879751275,177.91531037094873</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>-39.20874000180199,177.91491897816118</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>-39.20937129531741,177.91451039854928</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>-39.21002075387342,177.91418259195697</t>
+        </is>
+      </c>
+      <c r="W365" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0287/nzd0287.xlsx
+++ b/data/nzd0287/nzd0287.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W365"/>
+  <dimension ref="A1:W366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27843,6 +27843,81 @@
         <v>355.9</v>
       </c>
       <c r="W365" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-28 21:53:33+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>354.27</v>
+      </c>
+      <c r="C366" t="n">
+        <v>351.79</v>
+      </c>
+      <c r="D366" t="n">
+        <v>357.15</v>
+      </c>
+      <c r="E366" t="n">
+        <v>349.8</v>
+      </c>
+      <c r="F366" t="n">
+        <v>350.25</v>
+      </c>
+      <c r="G366" t="n">
+        <v>361.85</v>
+      </c>
+      <c r="H366" t="n">
+        <v>357</v>
+      </c>
+      <c r="I366" t="n">
+        <v>369.27</v>
+      </c>
+      <c r="J366" t="n">
+        <v>363.71</v>
+      </c>
+      <c r="K366" t="n">
+        <v>354.86</v>
+      </c>
+      <c r="L366" t="n">
+        <v>354.8</v>
+      </c>
+      <c r="M366" t="n">
+        <v>367.08</v>
+      </c>
+      <c r="N366" t="n">
+        <v>366.04</v>
+      </c>
+      <c r="O366" t="n">
+        <v>369.66</v>
+      </c>
+      <c r="P366" t="n">
+        <v>375.01</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>369.4</v>
+      </c>
+      <c r="R366" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="S366" t="n">
+        <v>376.37</v>
+      </c>
+      <c r="T366" t="n">
+        <v>368.02</v>
+      </c>
+      <c r="U366" t="n">
+        <v>357.45</v>
+      </c>
+      <c r="V366" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="W366" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27859,7 +27934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B367"/>
+  <dimension ref="A1:B368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31532,6 +31607,16 @@
       </c>
       <c r="B367" t="n">
         <v>-0.59</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-06-28 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -31700,28 +31785,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1298892904355373</v>
+        <v>-0.1299994918110074</v>
       </c>
       <c r="J2" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K2" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07104457114066365</v>
+        <v>0.07159545597503669</v>
       </c>
       <c r="M2" t="n">
-        <v>2.644575309159401</v>
+        <v>2.637781833024187</v>
       </c>
       <c r="N2" t="n">
-        <v>12.1928364556684</v>
+        <v>12.15953272929869</v>
       </c>
       <c r="O2" t="n">
-        <v>3.491824230351293</v>
+        <v>3.487052154657095</v>
       </c>
       <c r="P2" t="n">
-        <v>357.9523420037415</v>
+        <v>357.9534988531649</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31778,28 +31863,28 @@
         <v>0.0311</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0918507129617548</v>
+        <v>-0.09090086432877123</v>
       </c>
       <c r="J3" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K3" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03475207797541602</v>
+        <v>0.034260908041163</v>
       </c>
       <c r="M3" t="n">
-        <v>2.784384262547047</v>
+        <v>2.781507378107272</v>
       </c>
       <c r="N3" t="n">
-        <v>12.9514156252673</v>
+        <v>12.9234583209171</v>
       </c>
       <c r="O3" t="n">
-        <v>3.598807528233109</v>
+        <v>3.594921184242723</v>
       </c>
       <c r="P3" t="n">
-        <v>352.593759367065</v>
+        <v>352.5837882406729</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31856,28 +31941,28 @@
         <v>0.0361</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07920170084771239</v>
+        <v>0.07923523238835962</v>
       </c>
       <c r="J4" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K4" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02382112309351181</v>
+        <v>0.0239955750461438</v>
       </c>
       <c r="M4" t="n">
-        <v>2.951821239408758</v>
+        <v>2.943901781157943</v>
       </c>
       <c r="N4" t="n">
-        <v>14.20791233139536</v>
+        <v>14.16899592334582</v>
       </c>
       <c r="O4" t="n">
-        <v>3.769338447446097</v>
+        <v>3.764172674485831</v>
       </c>
       <c r="P4" t="n">
-        <v>354.9631747362657</v>
+        <v>354.9628227357276</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31934,28 +32019,28 @@
         <v>0.0411</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0763264068761066</v>
+        <v>0.07769001721263111</v>
       </c>
       <c r="J5" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K5" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02071327996820183</v>
+        <v>0.02156198861069458</v>
       </c>
       <c r="M5" t="n">
-        <v>3.08632932483837</v>
+        <v>3.084176027201244</v>
       </c>
       <c r="N5" t="n">
-        <v>15.22315628173904</v>
+        <v>15.19695992172411</v>
       </c>
       <c r="O5" t="n">
-        <v>3.901686338205448</v>
+        <v>3.898327836614579</v>
       </c>
       <c r="P5" t="n">
-        <v>345.3636044477457</v>
+        <v>345.349289818506</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32012,28 +32097,28 @@
         <v>0.0456</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1441093434804143</v>
+        <v>0.1458734978986658</v>
       </c>
       <c r="J6" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K6" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08552485295330281</v>
+        <v>0.08780801579424469</v>
       </c>
       <c r="M6" t="n">
-        <v>2.809064819153122</v>
+        <v>2.809483456329625</v>
       </c>
       <c r="N6" t="n">
-        <v>12.27320335216897</v>
+        <v>12.2655396572159</v>
       </c>
       <c r="O6" t="n">
-        <v>3.50331319641407</v>
+        <v>3.50221924745095</v>
       </c>
       <c r="P6" t="n">
-        <v>343.2897127434103</v>
+        <v>343.2711933645654</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32090,28 +32175,28 @@
         <v>0.0468</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1437053280519919</v>
+        <v>0.145369789737737</v>
       </c>
       <c r="J7" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K7" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09787796337000843</v>
+        <v>0.10032962778024</v>
       </c>
       <c r="M7" t="n">
-        <v>2.695323396870535</v>
+        <v>2.696601003444644</v>
       </c>
       <c r="N7" t="n">
-        <v>10.52010775804074</v>
+        <v>10.51439578858551</v>
       </c>
       <c r="O7" t="n">
-        <v>3.243471559616447</v>
+        <v>3.242590906757358</v>
       </c>
       <c r="P7" t="n">
-        <v>355.0753344558785</v>
+        <v>355.0578616109777</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32168,28 +32253,28 @@
         <v>0.0413</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01776806465976578</v>
+        <v>-0.01691051302473257</v>
       </c>
       <c r="J8" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K8" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001331633600568316</v>
+        <v>0.001213792315476692</v>
       </c>
       <c r="M8" t="n">
-        <v>2.853000600561851</v>
+        <v>2.849740124466332</v>
       </c>
       <c r="N8" t="n">
-        <v>13.08611945126077</v>
+        <v>13.05640154526881</v>
       </c>
       <c r="O8" t="n">
-        <v>3.617474181146394</v>
+        <v>3.613364297336874</v>
       </c>
       <c r="P8" t="n">
-        <v>355.9726258987031</v>
+        <v>355.963623668828</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32246,28 +32331,28 @@
         <v>0.0415</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01624220976311418</v>
+        <v>0.01594278824283962</v>
       </c>
       <c r="J9" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K9" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001026303442932641</v>
+        <v>0.0009953682708854217</v>
       </c>
       <c r="M9" t="n">
-        <v>3.136723755181772</v>
+        <v>3.129211937140901</v>
       </c>
       <c r="N9" t="n">
-        <v>14.19262007201148</v>
+        <v>14.15448404594039</v>
       </c>
       <c r="O9" t="n">
-        <v>3.767309394250952</v>
+        <v>3.762244548928257</v>
       </c>
       <c r="P9" t="n">
-        <v>369.3576595562458</v>
+        <v>369.3608027621415</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32324,28 +32409,28 @@
         <v>0.0443</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05173487850716262</v>
+        <v>0.05025287845301608</v>
       </c>
       <c r="J10" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K10" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008389093364737477</v>
+        <v>0.007963055197994673</v>
       </c>
       <c r="M10" t="n">
-        <v>3.466776362665883</v>
+        <v>3.463524114975219</v>
       </c>
       <c r="N10" t="n">
-        <v>17.48586873929867</v>
+        <v>17.45628342602683</v>
       </c>
       <c r="O10" t="n">
-        <v>4.181610782856132</v>
+        <v>4.178071735385455</v>
       </c>
       <c r="P10" t="n">
-        <v>364.9144425363586</v>
+        <v>364.9299999729225</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32402,28 +32487,28 @@
         <v>0.0429</v>
       </c>
       <c r="I11" t="n">
-        <v>0.05104313410564538</v>
+        <v>0.05026435626782285</v>
       </c>
       <c r="J11" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K11" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01318603555485554</v>
+        <v>0.01286985754466152</v>
       </c>
       <c r="M11" t="n">
-        <v>2.628141402619554</v>
+        <v>2.624356113083176</v>
       </c>
       <c r="N11" t="n">
-        <v>10.77679916181409</v>
+        <v>10.75233291072466</v>
       </c>
       <c r="O11" t="n">
-        <v>3.282803552120365</v>
+        <v>3.279075008401707</v>
       </c>
       <c r="P11" t="n">
-        <v>354.8524111679262</v>
+        <v>354.8605864623706</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32480,28 +32565,28 @@
         <v>0.0355</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.01121034106654994</v>
+        <v>-0.0125563187280317</v>
       </c>
       <c r="J12" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K12" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0005243376243279085</v>
+        <v>0.0006613340702940063</v>
       </c>
       <c r="M12" t="n">
-        <v>2.927383875280279</v>
+        <v>2.92647839749274</v>
       </c>
       <c r="N12" t="n">
-        <v>13.24015084072968</v>
+        <v>13.21898882640102</v>
       </c>
       <c r="O12" t="n">
-        <v>3.638701807063843</v>
+        <v>3.635792736997122</v>
       </c>
       <c r="P12" t="n">
-        <v>357.4606821277745</v>
+        <v>357.4748116563304</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32558,28 +32643,28 @@
         <v>0.0256</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1432936417322727</v>
+        <v>-0.1424069484516256</v>
       </c>
       <c r="J13" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K13" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04665102803899934</v>
+        <v>0.04638188289572809</v>
       </c>
       <c r="M13" t="n">
-        <v>3.659145635887181</v>
+        <v>3.652907456873438</v>
       </c>
       <c r="N13" t="n">
-        <v>23.19202145508265</v>
+        <v>23.13504015864143</v>
       </c>
       <c r="O13" t="n">
-        <v>4.815809532683227</v>
+        <v>4.809889828118876</v>
       </c>
       <c r="P13" t="n">
-        <v>369.3767000111043</v>
+        <v>369.367391864032</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32636,28 +32721,28 @@
         <v>0.0262</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.02705868633079946</v>
+        <v>-0.02772687481328943</v>
       </c>
       <c r="J14" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K14" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002297296009601379</v>
+        <v>0.002427368235032534</v>
       </c>
       <c r="M14" t="n">
-        <v>3.344567022181983</v>
+        <v>3.338594294754123</v>
       </c>
       <c r="N14" t="n">
-        <v>17.57485244135949</v>
+        <v>17.53042654844128</v>
       </c>
       <c r="O14" t="n">
-        <v>4.192237164254843</v>
+        <v>4.18693522142883</v>
       </c>
       <c r="P14" t="n">
-        <v>367.9335688987976</v>
+        <v>367.940583270963</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32714,28 +32799,28 @@
         <v>0.0255</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1199545282834307</v>
+        <v>-0.1194405574084879</v>
       </c>
       <c r="J15" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K15" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04165140135552448</v>
+        <v>0.04156849262865003</v>
       </c>
       <c r="M15" t="n">
-        <v>3.334597412846048</v>
+        <v>3.327905042581815</v>
       </c>
       <c r="N15" t="n">
-        <v>18.29874346281783</v>
+        <v>18.25081352503766</v>
       </c>
       <c r="O15" t="n">
-        <v>4.277703059215054</v>
+        <v>4.272097087501368</v>
       </c>
       <c r="P15" t="n">
-        <v>371.9822923717325</v>
+        <v>371.9768969135744</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32792,28 +32877,28 @@
         <v>0.0261</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1386381910571617</v>
+        <v>-0.1390558560831151</v>
       </c>
       <c r="J16" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K16" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05141226222950146</v>
+        <v>0.05202882178130175</v>
       </c>
       <c r="M16" t="n">
-        <v>3.660983237340592</v>
+        <v>3.652867085904739</v>
       </c>
       <c r="N16" t="n">
-        <v>19.6006574268425</v>
+        <v>19.54841216354442</v>
       </c>
       <c r="O16" t="n">
-        <v>4.427262972406598</v>
+        <v>4.421358633219479</v>
       </c>
       <c r="P16" t="n">
-        <v>379.4694881902464</v>
+        <v>379.4738726685924</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32870,28 +32955,28 @@
         <v>0.0267</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1603084812978841</v>
+        <v>-0.1623934667659548</v>
       </c>
       <c r="J17" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K17" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L17" t="n">
-        <v>0.07871610726520561</v>
+        <v>0.08094088505509567</v>
       </c>
       <c r="M17" t="n">
-        <v>3.262173624904585</v>
+        <v>3.263284331740308</v>
       </c>
       <c r="N17" t="n">
-        <v>16.62405430022687</v>
+        <v>16.61477188356918</v>
       </c>
       <c r="O17" t="n">
-        <v>4.077260636778923</v>
+        <v>4.076122162493315</v>
       </c>
       <c r="P17" t="n">
-        <v>377.3588447193638</v>
+        <v>377.3807320526776</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32948,28 +33033,28 @@
         <v>0.0328</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.02855669707474035</v>
+        <v>-0.03051968203792495</v>
       </c>
       <c r="J18" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K18" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002940845556233418</v>
+        <v>0.003372812515974655</v>
       </c>
       <c r="M18" t="n">
-        <v>3.029657121662723</v>
+        <v>3.031278939733635</v>
       </c>
       <c r="N18" t="n">
-        <v>15.28124494078871</v>
+        <v>15.2715218460309</v>
       </c>
       <c r="O18" t="n">
-        <v>3.909123295674966</v>
+        <v>3.907879456435536</v>
       </c>
       <c r="P18" t="n">
-        <v>382.7192764672059</v>
+        <v>382.7398830886126</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33026,28 +33111,28 @@
         <v>0.033</v>
       </c>
       <c r="I19" t="n">
-        <v>0.006616260978774491</v>
+        <v>0.005096923476891456</v>
       </c>
       <c r="J19" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K19" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0001241314555118223</v>
+        <v>7.408728186508728e-05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.129516134328927</v>
+        <v>3.127905337471715</v>
       </c>
       <c r="N19" t="n">
-        <v>19.48873159433149</v>
+        <v>19.45459378058218</v>
       </c>
       <c r="O19" t="n">
-        <v>4.414604353091168</v>
+        <v>4.410736194852531</v>
       </c>
       <c r="P19" t="n">
-        <v>378.8525735003702</v>
+        <v>378.868522890344</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33104,28 +33189,28 @@
         <v>0.036</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0368366224615093</v>
+        <v>0.03552033157047266</v>
       </c>
       <c r="J20" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K20" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L20" t="n">
-        <v>0.00401020703365107</v>
+        <v>0.003751590005892425</v>
       </c>
       <c r="M20" t="n">
-        <v>3.258400870270631</v>
+        <v>3.255222674019944</v>
       </c>
       <c r="N20" t="n">
-        <v>18.62695130483669</v>
+        <v>18.59037165028937</v>
       </c>
       <c r="O20" t="n">
-        <v>4.315895191595446</v>
+        <v>4.311655326007561</v>
       </c>
       <c r="P20" t="n">
-        <v>369.3373292670753</v>
+        <v>369.3511471559342</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33182,28 +33267,28 @@
         <v>0.0526</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1010757625258903</v>
+        <v>0.09962076681634173</v>
       </c>
       <c r="J21" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K21" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03817170854705976</v>
+        <v>0.03731413268166095</v>
       </c>
       <c r="M21" t="n">
-        <v>2.849919928016704</v>
+        <v>2.848324964197968</v>
       </c>
       <c r="N21" t="n">
-        <v>14.22800734619551</v>
+        <v>14.20668608303986</v>
       </c>
       <c r="O21" t="n">
-        <v>3.772003094669397</v>
+        <v>3.769175782984903</v>
       </c>
       <c r="P21" t="n">
-        <v>357.2877135007384</v>
+        <v>357.3029874566257</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33260,28 +33345,28 @@
         <v>0.0488</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.028372380391347</v>
+        <v>-0.03119672816398285</v>
       </c>
       <c r="J22" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K22" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L22" t="n">
-        <v>0.003178438185615917</v>
+        <v>0.003847301415282778</v>
       </c>
       <c r="M22" t="n">
-        <v>2.748672314663272</v>
+        <v>2.754576819837138</v>
       </c>
       <c r="N22" t="n">
-        <v>13.95369677827312</v>
+        <v>13.98200907547189</v>
       </c>
       <c r="O22" t="n">
-        <v>3.735464733908369</v>
+        <v>3.739252475491845</v>
       </c>
       <c r="P22" t="n">
-        <v>360.9110611284203</v>
+        <v>360.9407099878682</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33319,7 +33404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W365"/>
+  <dimension ref="A1:W366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76027,6 +76112,123 @@
         </is>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-28 21:53:33+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>-39.197026666930284,177.92021885892936</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>-39.197631686595315,177.91977153553242</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>-39.19826765270305,177.91940578793952</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>-39.1988478607969,177.91889987070144</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>-39.19944523342652,177.91843414424832</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>-39.2001039748012,177.91820308298577</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>-39.20077945922975,177.9180131851596</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>-39.201480120212366,177.91802362682915</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>-39.20216359370864,177.91783138777814</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>-39.20284405106593,177.91760406942493</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>-39.20349072551756,177.91728247207985</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>-39.20417080867769,177.91706350549345</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>-39.20480593728202,177.9167008121733</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>-39.20546447639198,177.91642295721056</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>-39.206132332575685,177.9161732021826</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>-39.206770032967846,177.91580292694047</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>-39.20744785648246,177.9156001367156</t>
+        </is>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>-39.20809955220753,177.91528757007237</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>-39.208736924212744,177.91490580666746</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>-39.209368707918536,177.91449957199492</t>
+        </is>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>-39.21001886801281,177.91417487369006</t>
+        </is>
+      </c>
+      <c r="W366" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
